--- a/유니티_노트.xlsx
+++ b/유니티_노트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40ACB955-5E5D-4C2F-91F0-77E115B01078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1F75D5-C249-4DA9-BF57-A5FA8603B8FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" firstSheet="2" activeTab="5" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" activeTab="12" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
   </bookViews>
   <sheets>
     <sheet name="디버깅" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="537">
   <si>
     <t>1.딜레이 주는 방식</t>
   </si>
@@ -71,1682 +71,1709 @@
     <t xml:space="preserve">        </t>
   </si>
   <si>
+    <t xml:space="preserve">    }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Update is called once per frame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void Update()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if (Input.GetMouseButtonDown(0))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            audioSource.Play();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            StartCoroutine(WaitForSceneLoad());</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        }</t>
+  </si>
+  <si>
+    <t>car project LoadScene.cs *참고</t>
+  </si>
+  <si>
+    <t>ex) if (transform.position.x &lt; -xRange)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            transform.position = new Vector3(-xRange, transform.position.y, transform.position.z);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // 오른쪽 경계를 넘어간 경우</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        else if (transform.position.x &gt; xRange)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            transform.position = new Vector3(xRange, transform.position.y, transform.position.z);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // 경계 내부에 있는 경우</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        else</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            horizontalInput = Input.GetAxis("Horizontal");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            transform.Translate(Vector3.right * Time.deltaTime * speed * horizontalInput);</t>
+  </si>
+  <si>
+    <t>Car Project PlayerController.cs *참고</t>
+  </si>
+  <si>
+    <t>1. 영역제한</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.local pc에 unity game 정보 저장하기. : PlayerPrefs 클래스 사용</t>
+  </si>
+  <si>
+    <t>local에 저장하면 좋은점</t>
+  </si>
+  <si>
+    <t>(1) 인터넷연결과 무관하다.</t>
+  </si>
+  <si>
+    <t>(2)프로그램 실행파일이 삭제되더라도 정보는 남아있다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)변수와 다르게 게임실행이 종료되더라도 메모리에서 사라지지 않는다. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">로칼에 저장하기 </t>
+  </si>
+  <si>
+    <t>PlayerPrefs.SetFloat("PMJ", rr.time)</t>
+  </si>
+  <si>
+    <t>로칼에서 가져오기</t>
+  </si>
+  <si>
+    <t>best = PlayerPrefs.GetFloat("PMJ") + 0.2f;</t>
+  </si>
+  <si>
+    <t>2.분산버전관리 : Git(혼자할때) GitHub(팀으로 할때) 구글드라이브</t>
+  </si>
+  <si>
+    <t>버전간 다른부분만 히스토리로 저장한다. 그래서 저장용량을  아낄수 있고, 버전간 이동이 자유롭다.</t>
+  </si>
+  <si>
+    <t>2-1 구글드라이브 백업 tip</t>
+  </si>
+  <si>
+    <t>(1).unity project 백업시 불필요한 폴더들(library,logs,UserSettings,obj,Build(s),Temp)은 삭제</t>
+  </si>
+  <si>
+    <t>(2) 공유하는법 : 점 세개를 누른다음에 사람모양 클릭 -&gt; 공유받을 사람의 이메일 주소를 입력 -&gt; 권한을 설정한다 -&gt; 보낸다.</t>
+  </si>
+  <si>
+    <t>(3) 공유 받은것 사용법 : 내 드라이브로 간다음에 왼쪽에 공유 문서함 폴더 안에 있음.</t>
+  </si>
+  <si>
+    <t>Assets 메뉴 &gt; Import package &gt; Custom Package &gt; 파일선택</t>
+  </si>
+  <si>
+    <t>3. 로칼에 있는 유니티 패키지 파일(.unitypackage) 임포트 하는 방법</t>
+  </si>
+  <si>
+    <t>1.다이나믹(중력 O)에서 키네마틱(중력X, 외력X)으로 바꾸기.</t>
+  </si>
+  <si>
+    <t>private void OnCollisionEnter(Collision collision)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        print("hello");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        GetComponent&lt;Rigidbody&gt;().isKinematic = true;</t>
+  </si>
+  <si>
+    <t>1-1 인스펙터창에서 바꾸는법(2차원) : rigidbody 2D 컴퍼넌트 -&gt; body type 클릭 -&gt; kinematic 선택</t>
+  </si>
+  <si>
+    <t>7.파티클 사용해서 이펙트 표시</t>
+  </si>
+  <si>
+    <t>(1)파티클 이펙트 = 작은 입자</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2) 파티클 이펙트 실행 ex) GetComponent&lt;ParticleSystem&gt;().Play(); </t>
+  </si>
+  <si>
+    <t>1. 제네릭, &lt;T&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)제네릭이 필요한 이유 : 다양한 종류의 컴포넌트에 대응하는 범용 자료형이 필요하기 때문이다. </t>
+  </si>
+  <si>
+    <t>(2) 제네릭형식 ex) GetComponent&lt;T&gt;();</t>
+  </si>
+  <si>
+    <t>2.월드 좌표계와 스크린 좌표계</t>
+  </si>
+  <si>
+    <t>(1)월드 좌표계 : 오브젝트의 위치 좌표계값의 기준의 되는 좌표계. 즉 유니티 에디터에서 사용하는 좌표계(고정 좌표계)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1-1)하이러라키창에 루트오브젝트(최상위 위치)는 월드좌표계를 기준으로 하고 서브 오브젝트는 그 상위 오브젝트를 기준좌표계(상대 좌표계)로 한다. </t>
+  </si>
+  <si>
+    <t>(1-2)서브 오브젝트 주의사항 : 처음부터 서브를 구성하지 말것. 왜냐하면 상대좌표계로 위치값을 설정해야 하는데, 쉽지가 않기 때문이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1-3) center와 pivot 위치가 같은 오브젝트(유니티 기본 오브젝트)에서 pivot위치를 다른위치로 바꾸는 방법 </t>
+  </si>
+  <si>
+    <t>a : 빈오브젝트(empty)를 만든다 b : 원래오브젝트를 empty의 서브로 만든다 c : 서브가 된 원래오브젝트의 좌표값을 원하는 pivot위치가 되도록 변경한다</t>
+  </si>
+  <si>
+    <t>a -&gt; b -&gt; c의 순서로 진행</t>
+  </si>
+  <si>
+    <t>(2)스크린 좌표계 : 디바이스 화면상의 기준 좌표계. 유니티 에디터에서 사용하는 좌표계가 아니라 디바이스상의 좌표계</t>
+  </si>
+  <si>
+    <t>(3) ex) Ray ray= Camera.main.ScreenPointToRay(Input.mousePosition);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Vector3 worldDir = ray.direction;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Bam.GetComponent&lt;BamController&gt;().Shoot(worldDir.normalized * 2000);</t>
+  </si>
+  <si>
+    <t>(4)ScreenPointToRay 메소드는 카메라 위치를 원점기준으로 하는 메소드이다. 그러므로 카메라와 날라가려는 오브젝트의 원점이 다르면 조정을 해줘야한다.</t>
+  </si>
+  <si>
+    <t>2. out 한정자</t>
+  </si>
+  <si>
+    <t>(1). out 한정자는 매개변수중에 결과값을 전달받는 매개변수(return값과 유사함)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2) ex)  public static void Out(out int num,out string name) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">            num = 50;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            name = "hello";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        static void Main(string[] args)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            int a;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            string name = "hi";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Out(out a, out name);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Console.WriteLine("num :" + a + "name :" + name);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        }  // C#용 코드</t>
+  </si>
+  <si>
+    <t>1. Ray 형 오브젝트</t>
+  </si>
+  <si>
+    <t>(1) Ray형 오브젝트는 콜라이더와 리지드바디 모두 기본적으로 가지고 있다.</t>
+  </si>
+  <si>
+    <t>2.Raycast 메소드</t>
+  </si>
+  <si>
+    <t>(1) Raycast 메소드는 리턴값이 bool형이다.</t>
+  </si>
+  <si>
+    <t>(2)충돌이 일어나면 True를 반환하고 안일어나면 False를 반환한다.</t>
+  </si>
+  <si>
+    <t>(3)Raycast 메소드 두번째 매개변수는 RaycastHit형을 쓴다.</t>
+  </si>
+  <si>
+    <t>4. Unity API</t>
+  </si>
+  <si>
+    <t>링크 : https://docs.unity3d.com/ScriptReference/</t>
+  </si>
+  <si>
+    <t>3-1 에러가 발생한다면 Project창의 Assets &gt; Standard Asstes &gt; Utillity 에서 에러가 발생한 스크립트를 찾아서 지운다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. RaycastHit</t>
+  </si>
+  <si>
+    <t>(1) RaycastHit은 Ray와 원점이 충돌한 지점의 정보를 가지고 있는 구조체 자료형</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)세번째 매개변수 인자는 카메라와 닿는 물체사이의 거리를 구해서 설정해준다. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   하지만 Mathf.Infinity를 쓰면 거리가 무한대 이기에 편하다.</t>
+  </si>
+  <si>
+    <t>5. 코드 분석법</t>
+  </si>
+  <si>
+    <t>(1) 절차적으로 위에서 아래로 내려가면서 봐라.</t>
+  </si>
+  <si>
+    <t>(2) 의심스러운 부분(if문,메소드 등등) 은 갖다대서 메소드 원형을 찾아봐라</t>
+  </si>
+  <si>
+    <t>(3) 그 메소드가 뭐하는 애인지 알고싶으면 구글링(UnityAPI)을 해봐라. stackoverflow(코딩계의 네이버 지식인) 사이트 참고</t>
+  </si>
+  <si>
+    <t>(4)코드 중간중간에 이상이 있는 부분을 print로 값을 찍고, 확인과정을 거쳐라.</t>
+  </si>
+  <si>
+    <t>(5) 검증과정이 끝나면 print를 지우거나 주석처리를 해라.</t>
+  </si>
+  <si>
+    <t>(6)코드에다가 중요한부분이나 문제가 되는 부분에 매우 자세히 주석을 달아놔라.</t>
+  </si>
+  <si>
+    <t>(7)노트필기 말고도 코드자체에 주석(주석은 10년후의 내가 욕하지않게 자세히 쉽게 풀어서 쓸데없는 얘기까지)을 달아라.</t>
+  </si>
+  <si>
+    <t>(번외)스크립트의 성질과 안맞는 코딩을 하지말것(아무데서나 다 할수있지만 아무데나 하지말고 가장 어울리는 스크립트를 찾아라)</t>
+  </si>
+  <si>
+    <t>3.ScreenPointToRay</t>
+  </si>
+  <si>
+    <t>(1) MainCamera를 원점를 원점으로 하는 메소드 이다.</t>
+  </si>
+  <si>
+    <t>1.OnTriggerEnter 메소드</t>
+  </si>
+  <si>
+    <t>(1)매개변수 other의 의미 : 충돌한 상대 오브젝트.</t>
+  </si>
+  <si>
+    <t>(1) 의미 : 스크립트에서 오브젝트를 식별하기 위한 수단</t>
+  </si>
+  <si>
+    <t>1.Tags</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 감각 저하</t>
+  </si>
+  <si>
+    <t>(2) 기억력 저하</t>
+  </si>
+  <si>
+    <t>(3) . ' . = 코딩 실력 저하</t>
+  </si>
+  <si>
+    <t>6.복붙을 하면 안돼는 이유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)원인 : 포멧이 맞지 않는 오디오 파일</t>
+  </si>
+  <si>
+    <t>(2) 해결방법 : 유니티에서 사용가능한 포멧으로 변환해준다. 사이트 링크 : https://online-audio-converter.com 에서 에러가 발생하는 오디오 파일을 변환시켜 준다</t>
+  </si>
+  <si>
+    <t>1.리소스 오디오 클립 에러</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)public(프로퍼티의 set,get의 기본 접근 지정자)</t>
+  </si>
+  <si>
+    <t>(2)private(attr(필드,메소드,프로퍼티)의 기본 접근지정자)</t>
+  </si>
+  <si>
+    <t>(3)internal(클래스 기본 접근지정자)</t>
+  </si>
+  <si>
+    <t>3.접근지정자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)이 메소드를 호출하는 스크립트가 삭제되더라도 재생을 보장함</t>
+  </si>
+  <si>
+    <t>(2)해보니까 코루틴 안써도 딜레이 줄수있음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ex ) </t>
+  </si>
+  <si>
+    <t>AudioSource.PlayClipAtPoint(clip, transform.position); //dodge 프로젝트 PlayerController.cs 55번 줄 참고</t>
+  </si>
+  <si>
+    <t>1.AudioSource.PlayClipAtPoint() 메소드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 프레임 간격 사이에 경과 시간</t>
+  </si>
+  <si>
+    <t>(2)de += Time.deltaTime; //프레임간에 경과시간을 누적하여 더함.</t>
+  </si>
+  <si>
+    <t>1.time.deltaTime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.하이러라키 창에 존재하는 게임오브젝트와 프로젝트창에 리소스는 다르다.</t>
+  </si>
+  <si>
+    <t>=프로젝트창의 리소스는 게임오브젝트가 아니다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)보안무시하고 삭제하기 예시) DestroyImmediate(삭제 할 컴포넌트,true);</t>
+  </si>
+  <si>
+    <t>2.컴포넌트 삭제하는 방법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)원인. 배열의 크기를 벗어나는 인덱스를 사용했다.</t>
+  </si>
+  <si>
+    <t>(2)해결법 : 25와 관련된 경우</t>
+  </si>
+  <si>
+    <t>if (AP.GetComponents&lt;Collider&gt;().Length != 0) //배열 사이즈를 체크해서 에러를 차단한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            DestroyImmediate(AP.GetComponents&lt;Collider&gt;()[0], true); //여기서 에러가 발생하는 경우</t>
+  </si>
+  <si>
+    <t>2.IndexOutOfRangeException: Index was outside the bounds of the array 에러 발생시 대처법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 기능 : 스크립트상에서 오브젝트의 컴포넌트를 추가해준다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2) 사용법 : gameObject.AddComponent(typeof(SphereCollider)); </t>
+  </si>
+  <si>
+    <t>(3) 잘못된 사용법 : gameObject.AddComponent( "SphereCollider" ) as SphereCollider; // 비추천 방식, 에러 가능성 있음(deprecated)</t>
+  </si>
+  <si>
+    <t>3.AddComponent 사용법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) deprecated : 권장안함. 향후 버전에서 존재하지 않을수 있음.</t>
+  </si>
+  <si>
+    <t>(2) legacy :  이전버전과의 호환성이나 기타 이유로 유지됨(살아있음) 권장안함.</t>
+  </si>
+  <si>
+    <t>7. deprecated 와 legacy 의 차이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 게임의 난이도를 조정하는 방법론 : 예시 오브젝트가 떨어지는 속도값, 어떤 오브젝트가 나올지 결정하는 확률값</t>
+  </si>
+  <si>
+    <t>(2) 레벨이란 : 게임의 스테이지 또는 난이도 등을 뜻함.</t>
+  </si>
+  <si>
+    <t>1.레벨 디자인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)Object 클래스의 메소드이다. 따라서 Object 클래스를 상속하고있기 때문에 어떤 자료형이든 쓸 수 있다.</t>
+  </si>
+  <si>
+    <t>(2)의미 : 참조변수를 문자열로 변환해준다.</t>
+  </si>
+  <si>
+    <t>(3)사용법 : float tume = 60.0f;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  tume.ToString("F1"); //Tume이 어떤자료형이든 Object 클래스의 메소드 이기 때문에 사용할 수 있다.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">F1의 의미 : 소수점 한자리까지 표시 </t>
+  </si>
+  <si>
+    <t>F2라면 두자리 까지 표시</t>
+  </si>
+  <si>
+    <t>매개변수 인자를 안적으면 원래 자릿수로 변환한다.</t>
+  </si>
+  <si>
+    <t>31. 기본자료형</t>
+  </si>
+  <si>
+    <t>(1) 기본자료형은 이름이 바뀐 형태이고 실체는 구조체이다.</t>
+  </si>
+  <si>
+    <t>(2) 예시 : float형의 실체는 struct Single 이다. int형은 struct Int32이다.</t>
+  </si>
+  <si>
+    <t>(3) 왜 저렇게 이름을 했을까 : 개발자들이 저이름에 익숙해져있기 때문에.</t>
+  </si>
+  <si>
+    <t>4. ToString 메소드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 의미 : 문자열끼리 더해서 새로운 문자열을 만들어 내는 방식 더하기 연산자 사용</t>
+  </si>
+  <si>
+    <t>(2) 예시 : PT.GetComponent&lt;Text&gt;().text = point.ToString()+ " point";</t>
+  </si>
+  <si>
+    <t>5. Concatenate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 의미 : this가 쓰인 그 클래스의 인스턴스를 의미함(이 클래스의 부모 클래스의 인스턴스는 base로 표현함)</t>
+  </si>
+  <si>
+    <t>(2) 사용처 : 매개변수랑 필드의 이름이 같을땐 this를 사용하는걸 써야만 함</t>
+  </si>
+  <si>
+    <t>(2) 예시 :this.sp = sp;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           this.speed = speed;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           this.ratio = ratio; //좋은 사용 예</t>
+  </si>
+  <si>
+    <t>sp = sp</t>
+  </si>
+  <si>
+    <t>speed = speed;</t>
+  </si>
+  <si>
+    <t>ratio = ratio;  //나쁜 사용 예</t>
+  </si>
+  <si>
+    <t>6. this</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 남아있는 컴퓨터 하드용량이 충분하지않으면 정상적인 빌드가 안될 수 있다.</t>
+  </si>
+  <si>
+    <t>3.안드로이드 빌드시 주의사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 에러가 발생하면 콘솔창에 에러가 표시됨 단 에러가 해결이 되더라도 콘솔창에 남아있기 때문에 주의해야함.</t>
+  </si>
+  <si>
+    <t>4.unity 에러 표시 주의사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 의미 : 텍스쳐(표면, 이미지) + 셰이더(색,질감,빛반사,굴절등)</t>
+  </si>
+  <si>
+    <t>(2) 만드는법 :프로젝트 창에서 우클릭을 한후 create -&gt; material 선택</t>
+  </si>
+  <si>
+    <t>3.머터리얼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>= 스케치 + 물감</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)center : 센터는 오브젝트의 중심점이 지형학적 중심</t>
+  </si>
+  <si>
+    <t>(2)pivot : 피봇은 발바닥이 기준점</t>
+  </si>
+  <si>
+    <t>4.center 와 pivot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)project 창에서 해당스크립트파일을 선택 </t>
+  </si>
+  <si>
+    <t>(2)우클릭</t>
+  </si>
+  <si>
+    <t>(3)reimport 클릭</t>
+  </si>
+  <si>
+    <t>5. 유니티 스크립트 public field가 에디터에서 안보일때</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)리지드 바디 컴퍼넌트 드래그를 납득하지 못함. 따져보니까 그동안 스크립트는 아무 이질감없이 드래그 해왔음 스크립트도 컴퍼넌트임</t>
+  </si>
+  <si>
+    <t>따라서 컴퍼넌트도 오브젝트, 스크립트처럼 드래그 할 수 있다.</t>
+  </si>
+  <si>
+    <t>5.내가 햇갈렸던 것들</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) AddForce를 사용하게 되면 관성력이 작용되고 그상태에서 방향전환을 하려면 관성력을 이겨야 하기 때문에 조작감이 나쁘다. 하지만 실제물리현상을 구현한다.</t>
+  </si>
+  <si>
+    <t>(2) velocity를 사용하게 되면 물리현상의 결과값을 바꿀 수 있기 때문에 관성력이 작용하더라도 무시가 가능하다. 그러므로 조작감이 좋다. 하지만 비현실적이다.</t>
+  </si>
+  <si>
+    <t>2. Rigidbody 와 AddForce 메소드와 velocity의 차이점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 의미 : GetAxis 의 매개변수값으로 문자열을 설정하게 되는데 그문자열은 edit -&gt; Project Settings -&gt; Input Manager -&gt; Axes 안에서 키별로 정의된 문자열들 중에서 선택해서 사용해야한다</t>
+  </si>
+  <si>
+    <t>즉 그 키를 조작했을때 GetAxis의 리턴값은 그 키가 Positve Button이면 0~1사이 값을 가지고 Negative Button 이면 0~(-1)사이 값을 가지고 그 키를 오래 누를수록 0에서 1또는 -1에 가까워 진다.</t>
+  </si>
+  <si>
+    <t>(1) edit -&gt; Project Settings -&gt; Input Manager -&gt; Axes 가서 size을 늘린다 맨마지막 스트링과 똑같은 복사본이 생긴다 그 복사본을 바꿔서 사용한다</t>
+  </si>
+  <si>
+    <t>(2-1) 주의점 : size 값이 axes 개수보다 작으면 axes가 삭제된다 따라서 함부로 size값을 줄이지 말자.</t>
+  </si>
+  <si>
+    <t>(2-2) 서로다른 Axes에 같은키를 배정하면 두Axes가 복수로 작동한다. 따라서 의도한게 아니라면 서로 다른 키값을 배정해 줘야 한다.</t>
+  </si>
+  <si>
+    <t>(2-3) 내가 만든 스크립트 말고 특정오브젝트는 오브젝트에서 자기 스스로 만들어 사용하는 스크립트가 존재한다. 그 스크립트 내부에서 Axes를 사용 할 수 있다. 예를 들면 UI를 사용하면 EventSystem 오브젝트</t>
+  </si>
+  <si>
+    <t>가 생기는데 얘가 StandaloneInputModule.cs가 생기고(내가 만든게 아님) 이안에서 Axes를 사용하고 있으므로 함부로 지우면 안된다. 만약에 지우면 ArgumentException: Input Button Submit is not setup~ 이런</t>
+  </si>
+  <si>
+    <t>에러가 발생한다(에러코드에서 나온 Submit Axes를 StandaloneInputModule.cs에서 사용하고 있기 때문에 함부로 지우면 안된다.)</t>
+  </si>
+  <si>
+    <t>4.Input.GetAxis 메소드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5. Axes 새로 만들기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 의미 : 현실세계의 사물을 단순화 시킨모델 (메모리를 차지않음 실제로 존재X)</t>
+  </si>
+  <si>
+    <t>(2) 사용법 : 인스턴스(클래스를 복제해서 만든 것, 메모리에 존재함으로 클래스와 달리 실체가 있다)를 사용해서 구현</t>
+  </si>
+  <si>
+    <t>(3) 자료형 : 모든클래스는 자료형이 될 수 있다.</t>
+  </si>
+  <si>
+    <t>7.클래스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 : 요소자료형이 다른 배열역할(메소드 포함)</t>
+  </si>
+  <si>
+    <t>7-1 구조체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)클래스 : 인스턴스가 heap영역에 저장되고 구조체의 데이터는 변수공간에 직접 저장됨 구조체는 가비지 컬렉션이 필요없음(운영체제가 지움)</t>
+  </si>
+  <si>
+    <t>(1)동적인 특성(변수는 저장공간이 무조건 1개)이 없기 때문에 클래스로 만들 필요가 없고, 성능적으로 heap영역보다 stack영역에서 사용하는게 더 좋음 따라서 구조체로 만듦.</t>
+  </si>
+  <si>
+    <t>(1) 의미 : 인스펙터창의 오브젝트의 이름옆에 체크표시(활성화 여부, 활성화 : 화면상에서'만' 보이는지 안보이는지 여부, 하이러라키창에선 그대로 남아있음)를 스크립트에서 제어 하는 메소드</t>
+  </si>
+  <si>
+    <t>(2) ex : gameObject.SetActive(false);</t>
+  </si>
+  <si>
+    <t>7-2 클래스와 구조체의 차이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7-3 기본자료형을 구조체로 만든 이유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.object.SetActive()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(1) 의미 : 첫번째 매개변수는 삭제 대상 오브젝트(하이러라키창에서도 삭제 즉 메모리에서 제거), 두번째 매개변수는 Destroy 메소드를 호출한시점에서 얼마뒤 삭제할건지 </t>
+  </si>
+  <si>
+    <t>(2) 사용예 : Destroy(gameObject, 3f); //이 스크립트를 가진 게임오브젝트를 삭제, 두번째 매개변수는 이 메소드가 호출되고 난뒤 3초뒤에 삭제</t>
+  </si>
+  <si>
+    <t>5.Destroy(Object x, float z);</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 : 메소드의 이름은 같지만 매개변수의 자료형이 다르거나 개수가 다른 메소드</t>
+  </si>
+  <si>
+    <t>(2)오버로딩이 존재하는 이유 : 오버로딩이 없다면 바디의 작업처리과정은 유사하지만, 매개변수가 다르거나 자료형이 다른 메소드를 별개의 메소드로 구성해줘야 한다.(다형성)</t>
+  </si>
+  <si>
+    <t>(1)의미 : 부모의 메소드를 자식클래스에서 재정의 해서 사용하는것, 같은 이름의 메소드가 서로 다르게 작동하게 할 수 있음(다양함의 파생)</t>
+  </si>
+  <si>
+    <t>(2)주의점 : 자식클래스에서 오버라이딩된 부모 클래스의 메소드는 무력화 된다.</t>
+  </si>
+  <si>
+    <t>(3)base : 부모를 의미. super</t>
+  </si>
+  <si>
+    <t>(1) 의미 : 최소한의 코드를 가지고 다양한 기능을 구현한다.</t>
+  </si>
+  <si>
+    <t>(2) 다형성을 구현하는 방법 : 오버로딩, 오버라이딩 등등</t>
+  </si>
+  <si>
+    <t>8.오버로딩(overloading)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9. 오버라이딩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10. 다형성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 의미 : 매개변수로 할당한 Transform 컴퍼넌트를 가지고 있는 오브젝트를 바라본다.</t>
+  </si>
+  <si>
+    <t>(2) 사용법 : bullet.transform.LookAt(target); //자세한 내용은 dodge 프로젝트에서 Spawner.cs 참고</t>
+  </si>
+  <si>
+    <t>(3) 대상오브젝트와 매개변수를 잇는 벡터가 대상오브젝트의 forward 프로퍼티가 된다.(dodge 프로젝트에서는 BulletController.cs의 forward값으로 사용된다.)</t>
+  </si>
+  <si>
+    <t>(1)의미 : T로(여기선 컴퍼넌트) 설정한 컴포넌트를 가진 오브젝트를 찾음 만약 컴포넌트를 가진 오브젝트가 존재 하지 않다면 예외(Exception)발생 예외는 런타임에러와 같다.</t>
+  </si>
+  <si>
+    <t>(1-2)스크립트내에서 다른오브젝트의 컴퍼넌트를 찾아야 할때 1.그 컴퍼넌트를 가진 오브젝트(GameObject.Find())를 써서 찾고, 2. 1번에서 찾은 object.GetComponuet() 써서 찾아야한다 그런데 이과정을 한번에 해주는 메소드다.</t>
+  </si>
+  <si>
+    <t>(2)사용예 :target = FindObjectOfType&lt;PlayerController&gt;().transform; //dodge프로젝트의 Spawner.cs 참고</t>
+  </si>
+  <si>
+    <t>6.대상오브젝트.transform.LookAt(Transform x, ); //오버로딩있음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.FindObjectOfType&lt;T&gt;()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 : 매개변수로 int 일때는 최대값 -1이고, float일때는 최대값도 포함해서 랜덤값을 리턴</t>
+  </si>
+  <si>
+    <t>11.Random.Range()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 의미 : 이 스크립트를 가진 오브젝트가 Scene창에 나타날때 호출된다.(게임이 시작할때 무조건 실행X)</t>
+  </si>
+  <si>
+    <t>8.Start()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 의미 : 프로그래밍에서 사용하는 Flag는 상태를 기록하고 제어하기 위한 boolean type(대체로 사용, 꼭 boolean을 사용할 필요 X)의 변수를 의미.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2) 예시 : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean flag = true; //초기값 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">while (flag) //초기에는 무한반복 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">      { </t>
+  </si>
+  <si>
+    <t xml:space="preserve">            input = scanner.nextInt();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            if ((input % 2) == 0) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                result += input;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">} </t>
+  </si>
+  <si>
+    <t>else { // else조건에 해당되는 순간 flag값이 바뀐다 따라서 무한반복이 종료되도록 처리함.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                System.out.println("======= " + input + " is Odd Number =======");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                flag = false;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            }</t>
+  </si>
+  <si>
+    <t>12.flag 변수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 : 유니티에서 제공해주는 데이터 배이스 '파일' 파일은 비휘발성인 HDD나 SSD에 저장된다(변수와 다르게 게임을 종료하거나 컴퓨터가 꺼져도 데이터 보존) 방대한 데이터는 저장용으로 적합하지않음</t>
+  </si>
+  <si>
+    <t>간단하고 개수가 적은 데이터들(예시 :게임정보, 상태정보) 저장하는데 사용 로컬에 저장되기 때문에 인터넷이 없더라도 사용가능</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2) 예시:   </t>
+  </si>
+  <si>
+    <t>if(surviveTime &gt; bestTime)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            bestTime = surviveTime;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            PlayerPrefs.SetFloat("BestTime", bestTime); //dodge프로젝트 gamedirector.cs 참고</t>
+  </si>
+  <si>
+    <t>(3)PlayerPrefs file 위치 : 윈도우 아이콘 우클릭 -&gt; 실행 -&gt; regedit 엔터 -&gt; HKEY_CURRENT_USER -&gt; Software -&gt; [company name] (만약 안적었다면 DefaultCompany) -&gt; [product name] (키값 이름 찾기)</t>
+  </si>
+  <si>
+    <t>텍스트로 저장이 아니라 바이너리(이진수)로 저장되어 있음.</t>
+  </si>
+  <si>
+    <t>9.PlayerPrefs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 예시 : 서버에 정보저장할때 구글 파이어 베이스 등을 사용, 키 : 벨류 방식으로 저장하는 JSon</t>
+  </si>
+  <si>
+    <t>(1) 유니티 허브 실행 -&gt; Add 클릭 -&gt; 프로젝트 폴더 찾아서 오픈</t>
+  </si>
+  <si>
+    <t>8.서버</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.유니티 허브에서 프로젝트 추가하는법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)3차원에서 이미지파일 스프라이트 생성하는 방법 : 가져오려는 이미지를 assets창에 올린뒤 이미지 클릭 -&gt; 인스펙터 창에서 Texture type -&gt; Sprite(2D and UI) 선택 -&gt; save</t>
+  </si>
+  <si>
+    <t>(2)안되는 이유 : 2차원 파일에선 비트맵이 스프라이트인데 3차원프로젝트에서는 비트맵이 defalt 타입으로 설정되서 안된다. 왜 그렇게 설정이 되는 이유는 2차원에선 비트맵이 쓰이는 용도가</t>
+  </si>
+  <si>
+    <t>UI용 이미지로 사용되기 때문에 처음부터 UI용타입인 스프라이트로 만들어 주지만 3차원에선 비트맵의 용도가 UI용 이미지가 아니라 3차원 모델에 텍스쳐를 입히는 용도로 사용되기 때문에</t>
+  </si>
+  <si>
+    <t>defalt로 설정이 된다 따라서 UI용으로 사용하려면 수동으로 Spirte 타입으로 변경해야 한다.</t>
+  </si>
+  <si>
+    <t>6. 3차원 프로젝트에서 2d ui요소를 만들때 이미지 파일이 연결이 잘 안될때</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) dodge 프로젝트 PlayerCotroller.cs 참고</t>
+  </si>
+  <si>
+    <t>6.키보드 버튼대신 UI버튼으로 대체하는 방법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 : value : 제한하려는 값</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           min :허용 가능한 최소값</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           max :허용 가능한 최대값</t>
+  </si>
+  <si>
+    <t>만약 value가 min보다 작다면 min값으로 보정, max보다 크다면 max로 보정 min에서 max사이값이면 그대로</t>
+  </si>
+  <si>
+    <t>(2)주의사항 : value값이 최소한 min과 max범위 중심으로 움직이는값을 해야한다 범위가 완전 다른값한테 쓰면 엉뚱한 값이 나올 수 있다. 따라서 어느정도 범위에 맞게 적용해놔야한다. dodge button UI 조정성</t>
+  </si>
+  <si>
+    <t>문제 발생(speed 값이 8로 했더니 이상했고 50정도로 했더니 해결됨)</t>
+  </si>
+  <si>
+    <t>10.mathf.clamp(float value,float min,float max)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 : 크기 + 방향을 두가지 물리량을 가지고 있음 (예: 속도,가속도,무게,힘...)</t>
+  </si>
+  <si>
+    <t>(2)정규화된 벡터(normalized vector) : 크기가 1인 단위벡터,방향벡터라고도 부른다.</t>
+  </si>
+  <si>
+    <t>(3)단위벡터 만드는법 : 단위벡터 = 벡터/벡터 크기(벡터크기 구하는법 : sqrt(벡터의 x성분^2 + 벡터의 y성분^2))</t>
+  </si>
+  <si>
+    <t>(3-1) 유니티 단위벡터 구하는법 : vector? 형 참조변수.normalized //?에는 Vector2,Vector3 등이 들어감 , Vector?형 참조변수.magnitude //벡터의 크기</t>
+  </si>
+  <si>
+    <t>(4)벡터의 합과 차를 구하는법 : 성분(x좌표끼리, y좌표끼리)끼리 더하거나 뺀다</t>
+  </si>
+  <si>
+    <t>(4-1) 유니티 합과 차 구하는 법 : Vector?형 참조변수 = Vector?형 참조변수 + Vector?형 참조변수</t>
+  </si>
+  <si>
+    <t>(5)벡터의 내적 : 내적값에 의해서 두벡터가 이루는 사잇각상태(몇도의 각을 갖고있는지)를 알아낼 수 있다.</t>
+  </si>
+  <si>
+    <t>(5-1) 유니티 벡터 내적 구하는법 : float c = Vector3.Dot(a,b); // Vector3.Dot() 는 두벡터(a,b)의 내적 구하는 메소드 구글드라이브의 벡터 표 참고</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6)벡터의 외적 : 두벡터가 이루는 평면이 수직의 벡터, 법선벡터(normal vector) </t>
+  </si>
+  <si>
+    <t>(6-1) 유니티 벡터 외적 구하는법 : Vector3 c = Vector3.Cross(a,b)</t>
+  </si>
+  <si>
+    <t>(6-2) 외적을 이용한 지면 식별 알고리즘</t>
+  </si>
+  <si>
+    <t>private void OnCollisionEnter2D(Collision2D collision) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // 바닥에 닿았음을 감지하는 처리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if (collision.contacts[0].normal.y &gt; 0.7f) //지면감지 알고리즘 : 지면의 이루는 각도가 45도 이하인 완만한 지면만 취급하는경우(벽,천장을 걸러낼 수 있다.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            isGrounded = true;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            jumpCount = 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   }</t>
+  </si>
+  <si>
+    <t>(7)모든벡터는 방향벡터 * 스칼라곱(배율)로 표현할 수 있다.</t>
+  </si>
+  <si>
+    <t>(7-1)유니티 스칼라곱 하는법 : Vector?형 참조변수 = Vector?형 * 스칼라값</t>
+  </si>
+  <si>
+    <t>(8) 유니티에서 벡터의 크기 구하는법 : float c = Mathf.Sqrt(0.27f * 0.27f + 0.53f * 0.53f + 0.8f * 0.8f); //Math.Sqrt 는 root</t>
+  </si>
+  <si>
+    <t>(9) 두벡터의 거리구하는 방법 : float d = Vector3.Distance(a, b); //거리만 관심있을때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(10)회전량을 나타내는 자료형 : Quaternion(쿼터니언 으로 발음) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(10-1) 회전에서 벡터를 쓸 수 없는 이유 : 두축이상의 동시 회전 계산 시 짐벌락 현상 오류 발생 두축이상 동시 회전 계산이 가능하도록 만들어 진게 쿼터니언이다. </t>
+  </si>
+  <si>
+    <t>(10-2) 벡터 to 쿼터니언 사용법 : Quaternion rotaion = Quaternion.Euler(new Vector3(0,60,0)); // rotaion은 참조변수, 스크립트창에서 로테이션값을 변경해야할때 사용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(10-3) 쿼터니언 to 벡터 사용법: Vector3 eulorRotation = rotaion.eulerAngles; // eulorRotation는 참조변수 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(10-4) 쿼터니언을 알아야 하는 이유 : 유니티 에디터에서 벡터3로 입출력을 처리해주지만 예를 들어서 trasform.rotation 같은 프로퍼티는 자료형이 Vector3가 아니라 Quaternion이기 때문에 쿼터니언에 대해서 </t>
+  </si>
+  <si>
+    <t>알고있어야 한다.</t>
+  </si>
+  <si>
+    <t>1.vector</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 : 크기 한가지 물리량만 가지고 있음(방향없음) (예: 질량,거리...)</t>
+  </si>
+  <si>
+    <t>2.scalar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)DEG(도) : degree (각도단위)</t>
+  </si>
+  <si>
+    <t>(2)RAD : radian (각도단위) 180도 = 파이rad</t>
+  </si>
+  <si>
+    <t>10. 계산기 약자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)전역변수(월드좌표계) 기준으로 동작하게 하는법 : 4번째 매개변수 인자로 Space.World를 넣어주면 됨 </t>
+  </si>
+  <si>
+    <t>11. 유니티 Transform 클래스 메소드(예 : Translate,Rotate...) defalt값(4번째 매개변수인자가 Space.Self로 설정)이 지역변수(지역좌표계 기준)으로 동작함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)C#같은 언어는 코드가 클래스 내부에서만 존재할 수 있다. 하지만 어떤 클래스에도 소속되지않는 attribute(필드,메소드 등)들은 원래는 클래스없이 만들어져야하는데 하지만 C#의 특성으로 인해</t>
+  </si>
+  <si>
+    <t>반드시 어떤 클래스 내부에서 만들어져야 하므로 아무 상관도없는 어떤 클래스 내부에 구성될 수 밖에 없다. 그런 attribute들은 소속클래스와 연관이 없음을 명시적으로 표시하기 위해서 static선언을 한다</t>
+  </si>
+  <si>
+    <t>(2) 따라서 static attribute들은 클래스의 인스턴스를 통해서 사용되는건 모순이다 C#에서는 static attribute들은 소속클래스 이름.static attribute 형식을 통해서 사용되어야 함</t>
+  </si>
+  <si>
+    <t>다른방식(인스턴스를 통한)을 사용하면 에러가 남(Java같은 언어에서는 허용함)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)static으로 선언된 attribute들은 RAM안에서 인스턴스내부가 아니라 DATA영역에 저장됨. 한번생기면 다신 안생김 </t>
+  </si>
+  <si>
+    <t>(4) Main에 선언된 static의 의미 : 만약 Main에 static이 안붙어있다면 Main메소드가 메모리에 올라가기 위해서 가장먼저 Main메소드를 포함하고 있는 클래스 인스턴스가 만들어져야 한다(New 연산자 사용)</t>
+  </si>
+  <si>
+    <t>인스턴스를 만들 주체가 없기 때문에 호출을 못하기 때문에 불가능하다 따라서 Main이 메모리에 못올라간다 이 프로그램을 실행했을때 O/S가 메인을 찾아야 하는데 Main이 없기 때문에 프로그램 실행이 안됨</t>
+  </si>
+  <si>
+    <t>따라서 Main에 static선언을 해줌으로써 프로그램 실행시 자동으로 가장먼저 메모리영역에 저장되도록 해주는 것이다. 두번째의미는 Main 메소드 특성상 프로그램의 시작과 끝을 지정해주는 메소드기 때문에</t>
+  </si>
+  <si>
+    <t>어느 클래스소속이라는게 어울리지 않는다 따라서 static선언을 해줌으로써 어떤 클래스와의 소속감을 분리시켜 준다. 그래서 static선언을 해주는게 어울린다.</t>
+  </si>
+  <si>
+    <t>13. static 선언</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.transform.position으로 값을 설정받을때 우항의 값은 전역공간 기준의 값으로 처리된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.transform.localPosition으로 값을 설정받을때 우항의 값은 현재 좌표계를 기준으로 처리된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 프로퍼티 : 로컬좌표계용 프로퍼티가 따로존재함(ex : local~~~)</t>
+  </si>
+  <si>
+    <t>(2)메소드 : 메소드의 매개변수는 무조건 로컬좌표계로 처리한다</t>
+  </si>
+  <si>
+    <t>5.transform.rotation으로 값을 설정받을때 우항의 값은 전역공간 기준의 값으로 처리된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.transform.localRotation으로 값을 설정받을때 우항의 값은 현재 좌표계를 기준으로 처리된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.transform.Translate()메소드로 값을 설정받을때 매개변수 값은 현재 좌표계를 기준으로 처리된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.transform.Rotate()메소드로 값을 설정받을때 매개변수의 값은 현재 좌표계를 기준으로 처리된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.transform의 메소드와 프로퍼티 좌표계 기준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.씬창에서 오브젝트 배치할때 무조건 루트위치에서 위치를 결정한후에 그다음에 서브로 옮기는짓을 맨마지막으로 한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)asset의 속성정보(인스펙터창의 속성항목 값들)을 저장하는 파일이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)유니티 에디터에선 보이지 않는다 </t>
+  </si>
+  <si>
+    <t>(3)meta파일을 지워버리면 그 에셋은 default값을 가진다.</t>
+  </si>
+  <si>
+    <t>8.meta파일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">        Vector3.forward : new Vector3(0,0,1) :고정좌표계를 기준으로 한다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Vector3.back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Vector3.up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Vector3.down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Vector3.left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Vector3.right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transform.forward : </t>
+  </si>
+  <si>
+    <t>transform.back :</t>
+  </si>
+  <si>
+    <t>transform.up</t>
+  </si>
+  <si>
+    <t>transform.down</t>
+  </si>
+  <si>
+    <t>transform.left</t>
+  </si>
+  <si>
+    <t>transform.right</t>
+  </si>
+  <si>
+    <t>10.Vector3 구조체의 속기(shorthand)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.transform 프로퍼티의 속기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)에셋폴더에서 스프라이트 선택</t>
+  </si>
+  <si>
+    <t>(2)인스펙터창에서 스프라이트 모드를 Multiple 선택후 apply버튼 클릭</t>
+  </si>
+  <si>
+    <t>(3)sprite editer 버튼을 눌러서 에디터창 띄우기</t>
+  </si>
+  <si>
+    <t>(4)slice 메뉴 선택 가로,세로 크기가 결정되있는 이미지들은 grid by cell size 선택후 낱개 이미지들의 가로,세로 픽셀값을 입력한후 slice버튼을 눌러 쪼갠다.</t>
+  </si>
+  <si>
+    <t>(4-2)(원본이미지 파일 우클릭 -&gt; 속성에서 픽셀사이즈를 체크한후 정확히 얼마로 쪼개야할지 체크해본다)</t>
+  </si>
+  <si>
+    <t>(5)스프라이트 가져와서 사용할때, 메타파일이 있다면 같이가져와야 자르는 작업을 편하게 할 수 있다(메타파일안에 자르기정보도 같이 포함되있기 때문이다)</t>
+  </si>
+  <si>
+    <t>1.spirt sheet 쪼개기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)유니티에서 Scene에 마이크 역할을 한다.</t>
+  </si>
+  <si>
+    <t>(2)Scene내에서 발생하는 모든 소리를 녹음한다. 즉 Audio Listener컴퍼넌트가 비활성화 되면 Scene내에서 발생하는 소리를 녹음할 수 없기 때문에 게임시작시 아무소리도 안들리게 된다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)유니티에서는 Scene하나에 Audio Listener가 한개만 작동함 </t>
+  </si>
+  <si>
+    <t>2.Audio Listener 컴퍼넌트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)75번과정을 통해서 스프라이트 쉬트(sheet)를 쪼갠다.</t>
+  </si>
+  <si>
+    <t>(2)Window -&gt; Animation -&gt; Animation -&gt;하이러라키창에서 에니메이션을 적용할 오브젝트 선택 -&gt; Create -&gt;에니메이션 클립이름 정해서 저장</t>
+  </si>
+  <si>
+    <t>(3)스프라이트 쉬트를 끌어서 타임라인에 배치 -&gt; 타임라인 오른쪽상단 점세개를 클릭 -&gt; Show sample rate 선택 -&gt; 재생하고 samples값을 조정하여 적당한값을 결정</t>
+  </si>
+  <si>
+    <t>(1)에니메이터 창에서 드래그 하는방법 : 가운데 휠버튼 누른상태로 이동</t>
+  </si>
+  <si>
+    <t>(2)유니티에서의 유한상태머신의 상태의 의미 = 애니메이션클립</t>
+  </si>
+  <si>
+    <t>(3)Entry : 게임이 시작되면 엔트리에서 나가는쪽의 연결된 상태(애니메이션)가 실행된다(기본상태) (연결하고싶은 상태를 우클릭후 -&gt; Set as Layer Default State)</t>
+  </si>
+  <si>
+    <t>(4)any state : 화살표조건(현재상태는 상관X)만 만족하면 연결된 상태로 바로 바뀜</t>
+  </si>
+  <si>
+    <t>(5)Exit : exit는 exit에서 나가는화살표(Make Transition존재안함)를 못만들고 들어가는 화살표만 만들수 있다.(exit는 마지막으로 실행되는 상태이므로 exit에서 다른상태로 전이가 안된다) 잘사용X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6)화살표 지우는법 : 지우고자하는 화살표 클릭 -&gt; 키보드 "Delete"키 </t>
+  </si>
+  <si>
+    <t>(7)파라미터(애니메이터창에서 조건만들때 쓰이는변수) 만드는법 : 애니메이터창 왼쪽상단 Parameters 탭 클릭 -&gt; +버튼클릭 -&gt; 파라미터 자료형선택후 생성(이름은 임의로)</t>
+  </si>
+  <si>
+    <t>(7-1)파라미터의 오른쪽 체크표시는 게임이 실행되고 나서 유니티가 관리한다.</t>
+  </si>
+  <si>
+    <t>(8)화살표 조건 만드는법 :(8(</t>
+  </si>
+  <si>
+    <t>(9)has exit time 의미 : 체크를하면 settings에 exit time을 설정할수있는데, 조건을 만족해도 exit time을 채운뒤에 전이된다.(딜레이시간동안 이전의 애니메이션이 계속 실행)</t>
+  </si>
+  <si>
+    <t>(10)Transition Duration 의미 : 블렌딩시간(두 애니메이션의 중간 과정)을 설정, 2차원에선 지원안됨</t>
+  </si>
+  <si>
+    <t>(11)Conditions :  +버튼을 누르면 (7)에서 만들어뒀던 파라미터들을 이용해서 조건을 구성하면 된다. 그리고 파라미터의 값들은 스크립트코드에서도 사용가능</t>
+  </si>
+  <si>
+    <t>(12)Animator 클래스형 참조변수.SetBool() 메소드 : 첫번째 매개변수는 애니메이터창에있는 파라미터를 뜻함 두번째 매개변수로 첫번째 매개변수값에 대입 ex) animator.SetBool("Grounded", isGrounded);</t>
+  </si>
+  <si>
+    <t>(13)Animator 클래스형 참조변수.SetTrigger() 메소드 : 매개변수로 들어간 트리거형 파라미터를 활성화시킴</t>
+  </si>
+  <si>
+    <t>(14)Text애니메이션 만드는 예 : Window -&gt; Animation -&gt; Animation -&gt; 하이러라키창에서 에니메이션을 적용할 오브젝트 선택 -&gt; Create -&gt; add property -&gt; 오브젝트 별로 제공되는 프로퍼티중에 내가 활용할 프로퍼티를 선택한다(예 : gameobject형의 position)</t>
+  </si>
+  <si>
+    <t>2.에니메이션 스프라이트 쉬트로 에니메이션 클립 만들기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.유한상태머신(finite state machine)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) 생성자를 호출해서 인스터스를 만드는 시점 : 리소스를 씬으로 드래그하는순간. 그결과물로 만들어진 인스턴스들의 목록을 보여주는게 하이러라키창이다</t>
+  </si>
+  <si>
+    <t>(2)awake 콜백시점 : 씬창에 있는 오브젝트들이 전부 로딩된후. start()보다 빠른호출을 보장함. 그러므로 필드 초기화할때 유용함.</t>
+  </si>
+  <si>
+    <t>12. Awake()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)리턴값없이 함수를 종료하는역할 : if문의 바디안에서 함수를 종료해야할 필요가 있을때 리턴을 써야 함수가 끝남.</t>
+  </si>
+  <si>
+    <t>14.return()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)마우스버튼을 누르다가 땐순간 1번만 호출</t>
+  </si>
+  <si>
+    <t>13.Input.GetMouseButtonUp()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)2 by 3 의미 : 화면을 씬창,게임창,하이러라키창으로 나눔</t>
+  </si>
+  <si>
+    <t>9.Layer 오른쪽끝에있는 버튼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.창 추가하는법 : 씬창 우클릭 -&gt; add tap -&gt; 추가하고싶은 창 선택</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) == 연산자 : 기본자료형일땐 값을 비교 레퍼런스(클래스)형일땐 주소값비교(C언어는 클래스자료형이 없기 때문에 데이터비교할때도 쓰고 포인터 변수의 주소값 비교할때도 쓴다.)</t>
+  </si>
+  <si>
+    <t>(2) equals메소드 : 레퍼런스형 변수의 데이터 비교할때(C언어는 클래스를 사용하지 않으므로 해당안됨)</t>
+  </si>
+  <si>
+    <t>15. ==연산자와 equals메소드 차이점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 : 충돌할때 생기는 배열</t>
+  </si>
+  <si>
+    <t>(2)배열의 인덱스로 0번을 주로 쓴다 왜냐하면 현실적으로 동시에 두개이상의 충돌포인트를 갖는게 힘들기 때문이다.</t>
+  </si>
+  <si>
+    <t>(3)ex ) private void OnCollisionEnter2D(Collision2D collision) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)의미 : 어떤 동일한 오브젝트가 대량으로 사용될때 사용한다. 또는 비슷한애지만 조금의 변형이 있는 오브젝트 씬에 존재하지않는 프리팹은 인스턴스가 아니다. </t>
+  </si>
+  <si>
+    <t>얘를 사용해서 작업처리를 하고싶으면 먼저 인스턴스화 시킨다음에 사용해야 한다. 예를 들면 Instanitiate()를 사용하여 구현</t>
+  </si>
+  <si>
+    <t>(2)만드는법 : 하이러라키창에 있는 오브젝트를 프로젝트창에 옮긴후 -&gt; 코드에서 작성 -&gt; 퍼블릭 필드에 프로젝트로 옮긴 오브젝트를 연결해준다.</t>
+  </si>
+  <si>
+    <t>(3)코드 : PublicAPIAttribute GameObject Spike;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        float span = 1.0f;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        float delta = 0;</t>
+  </si>
+  <si>
+    <t>private void Update() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        delta += Time.deltaTime;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if(DeltaSpeed &gt; span)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            DeltaSpeed = 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            GameObject go = Instantiate(spike);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            int px = Random.Range(-6, 7);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            go.transform.position = new Vector3(px,7,0);</t>
+  </si>
+  <si>
+    <t>}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.collision.contact[] </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15. Prefabs(프리팹 복제)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)주의사항 : 2D프로젝트에서는 콜백안됨.</t>
+  </si>
+  <si>
+    <t>(2)2D프로젝트에선 2D형 컴퍼넌트,메소드를 사용할것 예외는 vector3</t>
+  </si>
+  <si>
+    <t>2.OnCollisionEnter()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)SortingLayer로 정렬하기 : Sprite Renderer 컴퍼넌트 -&gt; Sorting Layer -&gt; Add Sorting Layer -&gt; +버튼클릭 -&gt; Layer추가(숫자가 높을수록 앞에 있고 낮을수록 가려진다) -&gt;각 오브젝트 선택후Sorting Layer값선택</t>
+  </si>
+  <si>
+    <t>11.레이어로 정렬하기(오브젝트들이 화면에 겹쳐지는 순서)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)오브젝트 크기구하는 방법 : 콜라이더를 씌워본다. -&gt; 콜라이더의 사이즈값을 체크한다 ex) 사각형오브젝트에 박스콜라이더를 씌워서 사이즈 체크</t>
+  </si>
+  <si>
+    <t>2.배경이어붙이기(Crankie Box)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)메인 카메라 -&gt; background -&gt; 스포이드 눌러서 배경색 찍기</t>
+  </si>
+  <si>
+    <t>12.메인카메라 배경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)stackoverflow</t>
+  </si>
+  <si>
+    <t>(2)github</t>
+  </si>
+  <si>
+    <t>11.개발자가 알아야하는 사이트 목록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)Canvas 오브젝트 선택 -&gt; 인스펙터창에서 Canvas Scaler 컴퍼넌트의 UI Scale Mode를 scale with screen size 선택 -&gt; 내가 설치하려는 디바이스 해상도를 입력(비율로 적어도 OK) </t>
+  </si>
+  <si>
+    <t>(2)UI Scale Mode를 Constant Pixel Size로 선택하면 유니티에디터에서 보이는대로 안보일 확률이 크다 따라서 scale with sreen size를 선택해야 한다.(가장 선호도높은 디바이스를 찾은뒤 걔를 기준으로 UI를 구성한다)</t>
+  </si>
+  <si>
+    <t>1. 유니티 에디터에서 보이는대로 실제 디바이스에서 UI가 보이게 하는 방법(유니티에디터에서는 실제디바이스에서 보이는거랑 다를 수 있다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)모니터 픽셀 하나하나에 컬러값(RGBA A는 투명도)을 구하는 연산순서를 정의한것 따라서 이순서에 맞춰 연산을 해야된다. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">예 )60Hz짜리 해상도 1920X1080 모니터의 경우 픽셀이 약 207만개, 60분의 1초마다 207만개의 픽셀의 컬러값을 계산해야 한다. 이계산과정은 GPU에서 수행한다. </t>
+  </si>
+  <si>
+    <t>예) 고성능 게임의 경우(조명환경이 복잡하거나 시시각각으로 환경이 변하는 경우) 각픽셀에 컬러값을 계산하는데 굉장히 많은 연산작업이 필요하게 된다. 따라서 모니터 주파수 60분의 1초마다 출력해야하는데</t>
+  </si>
+  <si>
+    <t>그걸 처리못해 버벅거리는 현상이 버퍼링 현상이다.</t>
+  </si>
+  <si>
+    <t>1. 렌더링 파이프라인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)기본적으로 scale with size모드를 사용해야 하며, 해상도 비율이 다른 디바이스에 대응하기 위해 UI 요소들으 배치가 가로방향 위주이면 Match값을 width &gt; height로 구성해주고, 세로방향 위주이면</t>
+  </si>
+  <si>
+    <t>Match값을 width &lt; height로 구성해준ㄴ다. 동일한 해상도 비율의 디바이스 간에는 Match값이 의미가 없음 Match값은 유니티 에디터에서 기준으로 삼은 해상도 비율과 다른 디바이스에 해당 앱이</t>
+  </si>
+  <si>
+    <t>설치되었을때 UI의 배치가 어떤식으로 조정할것인지에 대한 factor(어떤요인이 되는 변수)값임 따라서, 유니티 에디터에서 기준으로 삼은 해상도 비율과 일치하는 디바이스에서는 Match값은 의미가 없다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.Canvas 옵션설정 방법 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)메모리상에 오직 인스턴스가 하나만 존재해야 하는 클래스 (예를들면 장치의 부품들처럼 하나만 존재하는 부품을 소스코드에서 가져다 사용해야 될 경우 그부품 클래스의 인스턴스가 여러개 존재하는것은 모순이다.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)만드는 방법 : 생성자를 private으로 만든다( private Store() { } ) -&gt; static 필드로 객체 생성(  private static   Store instance = new Store(); ) </t>
+  </si>
+  <si>
+    <t>-&gt; 객체의 getter 구현( public static Store getInstance() {return instance}</t>
+  </si>
+  <si>
+    <t>(3)유니티에서 싱글톤 만드는법 :</t>
+  </si>
+  <si>
+    <t>16.싱글톤(single tone)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)추상클래스는 추상메소드(추상메소드는 바디가없고 선언부만 있는 메소드)를 가지고있는 클래스</t>
+  </si>
+  <si>
+    <t>(2)추상클래스를 상속한 자식클래스에서 그 추상메소드를 오버라이딩해서 추상메소드를 사용할 수 있는 메소드로 만든다.(구현) extends사용</t>
+  </si>
+  <si>
+    <t>(3)단,  자식클래스에서 추상클래스의 추상메소드를 오버라이딩 할 의무는 없다(선택이다  extends 사용)</t>
+  </si>
+  <si>
+    <t>(1)상수,추상메소드(추상메소드는 바디가없고 선언부만 있는 메소드)만 가지고있는 클래스 필드,일반메소드는 존재할 수 없음.</t>
+  </si>
+  <si>
+    <t>(2)자식인터페이스에서 상속 가능(extends) 자식인터페이스끼리 상속</t>
+  </si>
+  <si>
+    <t>(3)자식클래스에서 상속하는경우 반드시 추상클래스의 추상메소드를 의무적으로 구현해줘야함(implements 사용)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4)추상클래스와의 차이점 : 추상메소드의 구현을 자식클래스에서 강제적으로 하면 인터페이스, 선택이면 추상클래스 이다. 그리고 추상클래스와 인터페이스는 공통적으로 다형성(오버라이딩,오버로딩) 구현의 수단이다. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">다만 인터페이스가 추상클래스보다 더 강제성을 띈다. </t>
+  </si>
+  <si>
+    <t>(1)사용법 : 참조변수.GetHashCode()</t>
+  </si>
+  <si>
+    <t>17.추상 클래스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18.인터페이스(interface)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>19.인스턴트의 주소값을 알려주는 메소드(GetHashCode())</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 : 게임시작시 필요한 오브젝트를 미리 만들어서 특정영역(게임화면 밖)에 배치해두고 필요할때마다 갖다쓰고 다쓰면 원래위치로 반환 게임실행중에 해당오브젝트가 새로 생성되거나 삭제되지 않는다.</t>
+  </si>
+  <si>
+    <t>(2)프리팹공장 방식과의 차이점 : 오브젝트를 미리만들지않고 게임실행중에 필요할때마다 Instantiate()를 사용해서 복제하고 필요없으면 Destroy()메소드로 삭제한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)장단점 : 장점은 게임실행중에 삭제(가비지 컬렉션)작업이 없기 때문에 쾌적하다. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">단점 : 게임시작시에 오브젝트를 만드는데 로딩시간이 필요하다.(프리팹공장방식에선 Destroy()메소드를 호출하여 삭제하는것이 실질적으로는 가비지컬렉션 작업이 발생하는것 이며 가비지컬렉션은 </t>
+  </si>
+  <si>
+    <t>메인쓰레드(어떤 주작업영역(UI나 핵심적인 작업등)상에서 작업처리가 되기 때문에 게임이 중지된다. 사용자가 느끼기에 버퍼링이 생기는것 처럼 느끼게 된다.)</t>
+  </si>
+  <si>
+    <t>3.오브젝트 풀링(object pooling)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)특징 : 배열인데도 배열명이 상수가 아니라 참조변수이다.</t>
+  </si>
+  <si>
+    <t>(2)만드는법 : GameObject[] platforms = new GameObject[count]; // new연산자를 사용한다. 즉 우항의 배열공간이 heap영역에 생긴다. 그리고 그것뿐만이 아니라 결론적으로 클래스 인스턴스 처럼 생긴다. 그안에 배열데이터가 들어간다</t>
+  </si>
+  <si>
+    <t>20. c#에서의 배열</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LLVM ERROR: IO failure on output stream: No space left on device</t>
+  </si>
+  <si>
+    <t>PLEASE submit a bug report to https://github.com/android-ndk/ndk/issues and include the crash backtrace.</t>
+  </si>
+  <si>
+    <t>Stack dump:</t>
+  </si>
+  <si>
+    <t>Program arguments: "C:/Program Files/Unity/Hub/Editor/2022.3.17f1/Editor/Data/PlaybackEngines/AndroidPlayer/NDK/toolchains/llvm/prebuilt/windows-x86_64/bin/llvm-objcopy.exe" --only-keep-debug Library/Bee/artifacts/Android/libunity/armeabi-v7a/unstripped/libunity.so Library/Bee/artifacts/Android/libunity/armeabi-v7a/libunity.dbg.so</t>
+  </si>
+  <si>
+    <t>UnityEngine.GUIUtility:ProcessEvent (int,intptr,bool&amp;)</t>
+  </si>
+  <si>
+    <t>(1)원인 : 하드용량 부족</t>
+  </si>
+  <si>
+    <t>(2)대처법 : 이런 에러싸인이 나오면 pc의 하드용량이 모자란지 확인해본다. 하드용량을 충분히 잡아준뒤 다시 빌드한다.</t>
+  </si>
+  <si>
+    <t>(1)원인 : 같은 프로젝트안에 동명의 Camera 스크립트가 존재 하기때문(Camera.mainScreenToWorldPoint(Input.mousePosition); 이 메소드를 호출할때 유니티에서 제공하는 Camera클래스와 이름이 같기때문에 에러가 발생)</t>
+  </si>
+  <si>
+    <t>(2)대처법 : 유니티 라이브러리에서 제공하는 클래스이름과 같은 이름으로 스크립트를 만들지 않는다.(좋은이름 짓는 방법 : 지으려는 이름에 _자기이름을 같이 사용한다거나 해서 겹치지않게 한다.)</t>
+  </si>
+  <si>
+    <t>6.Building Library\Bee\artifacts\Android\libunity\armeabi-v7a\libunity.dbg.so failed with output:</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6-1 Assets\Script\slingShotScript.cs(32,50): error CS0117: 'Camera' does not contain a definition for 'main'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 : 매개변수로 설정한 디바이스상(스크린좌표계,픽셀단위를 사용)의 좌표를 유니티의 월드좌표계(유니티 자체 단위계(눈금))로 변환해준다 단, Z값은 카메라의 Z값으로 반환 즉 카메라랑 선상에 있어서 안보인다</t>
+  </si>
+  <si>
+    <t>(2)대처법 : 2D일때는 vector2로 명시적형변환을 해준다.</t>
+  </si>
+  <si>
+    <t>(2-1) 예시 스크립트 : transform.position = (Vector2)Camera.main.ScreenToWorldPoint(Input.mousePosition);</t>
+  </si>
+  <si>
+    <t>7. Camera.main.ScreenToWorldPoint();</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)의미 :  오브젝트의 궤적(발자취)을 그려주는 컴퍼넌트</t>
+  </si>
+  <si>
+    <t>(2)사용법</t>
+  </si>
+  <si>
+    <t>(2-1) Materials : 설정안하면 기본값으로 보라색 색종이(사각형)으로 나옴 머터리얼을 다른값으로 설정하면 머터리얼대로 나옴 단, 레이어 정렬이 적용되는것과 안되는것이 있음 적용되는것은 파티클만 가능</t>
+  </si>
+  <si>
+    <t>1.Trail Renderer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)setActive는 GameObject클래스 소속의 메소드고 GameObject클래스 + 상속한 자식클래스의 참조변수에서만 사용할 수 있다. 따라서 GameObject와 상속관계가 없는 Component형 참조변수(예 : TraillRenderer)를 통해서는 호출 할 수 없다</t>
+  </si>
+  <si>
+    <t>(2)따라서 Component형 참조변수를 활성화시키거나 비활성화 시킬때는 SetActive를 사용할 수 없고, Component클래스에서 제공하는 enabled 프로퍼티를 사용해서 활성화,비활성화 처리를 할 수있다.</t>
+  </si>
+  <si>
+    <t>16. setActive와 Enabled의 차이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)동기식(sync) : 동기식은 메소드가 호출되면 메소드가 실행종료될때까지 다음라인으로 안넘어가고 대기상태</t>
+  </si>
+  <si>
+    <t>(2)비동기식(async) : 비동기식은 메소드호출되고 메소드의 종료 여분상관없이 다음라인으로 넘어감 (예시: StartCoroutine)</t>
+  </si>
+  <si>
+    <t>21.메소드의 동작방식(동기식,비동기식)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)GameObject클래스와 아무런 상속관계가 없다. 따라서 서로간에 형변환이 불가능하다. </t>
+  </si>
+  <si>
+    <t>(2)하지만 Unity에서는 Scene에 추가된 모든자로형은 GameObject형으로도 취급되므로 형변환이 가능하다. UNITY에서만 해당</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.UI 자료형(예 : Slider) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)힘의 공식 : F = ma // f는 힘,m은 질량, a는 가속도 </t>
+  </si>
+  <si>
+    <t>(1)E = mc^2 // E는 에너지,m는 질량,c는 광속도</t>
+  </si>
+  <si>
+    <t>(1) 하는법 :</t>
+  </si>
+  <si>
+    <t>3.뉴턴의 운동방정식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5.Rigidbody 컴퍼넌트 질량값 조절</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.아인슈타인의 에너지 공식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1) if(!(collision.gameObject.tag.Equals("Ground"))) //코드의 맨앞부분에 적는다 햇갈린다면 ()를 사용해서 명시적으로 구분을 해줄것</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            x.SetTrigger("New Trigger");</t>
+  </si>
+  <si>
+    <t>22. !(not) 붙이는위치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)일단 필요한 자료형 이름을 소스코드에 적는다(using이 안되있다면 빨간줄이 그어진다)</t>
+  </si>
+  <si>
+    <t>(2)빨간줄 그어지고 빨간색 X아이콘이 나타나고 그걸 클릭한다</t>
+  </si>
+  <si>
+    <t>(3)목록으로 오류사항을 해결할수 있는 해결책을 제시해준다 그중에서 선택한다.</t>
+  </si>
+  <si>
+    <t>1.자료형의 namespace가 기억안날때</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)https://jinhyo98.tistory.com/436 참고</t>
+  </si>
+  <si>
+    <t>12.폴더내 특정 키워드를 가진 파일찾기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)게임오브젝트 : 유니티 내에서 사용하는 고유 좌표계</t>
+  </si>
+  <si>
+    <t>(2) UI : 스크린좌표계(픽셀)</t>
+  </si>
+  <si>
+    <t>4. 게임오브젝트와 UI단위계(좌표계) 차이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>public class Score : MonoBehaviour</t>
+  </si>
+  <si>
+    <t>{</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    GameObject G;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Text T;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Start is called before the first frame update</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void Start()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        print(gameObject);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        T = GetComponent&lt;Text&gt;(); //26번 라인의 RectTransform형 position 프로퍼티를 사용하기 위해서 찾는다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                  //왜냐하면 gameobject형에서는 RectTransform을 쓸수 없기 때문이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        print(T);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        T.rectTransform.position = Camera.main.WorldToScreenPoint(G.transform.position);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    } /* scene좌표계의 돼지좌표값을 UI좌표계로 변환한 우항의 값을 Text UI좌표값으로 대입을 시키려면 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">       * 좌항의 UI의 좌표값(position)으로 UI의 좌표계 자료형인 RectTransform형 position 프로퍼티를 사용해야 한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       * 만약 Transform형 position 프로퍼티를 좌항에서 사용하면 Text UI좌표값이 정상적으로 설정되지 못한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       * 왜냐하면 Transform형 position 프로퍼티는 게임오브젝트의 위치값을 설정할때 사용하는 프로퍼티이고 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">       * UI의 위치값을 설정할때는 사용할 수 없기 때문이다 UI의 위치값을 설정할때는 반드시 RectTransform형</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       * position 프로퍼티를 사용해야 한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       */</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. Scene좌표계와 월드좌표계 변환방법 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">        G = GameObject.Find("small_helmet_pig_sprites_by_chinzapep-d57z4bs_0");</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t xml:space="preserve">        SceneManager.LoadScene("GameScene");</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    }</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    // Update is called once per frame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    void Update()</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        if (Input.GetMouseButtonDown(0))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            audioSource.Play();</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            StartCoroutine(WaitForSceneLoad());</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        }</t>
-  </si>
-  <si>
-    <t>car project LoadScene.cs *참고</t>
-  </si>
-  <si>
-    <t>ex) if (transform.position.x &lt; -xRange)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            transform.position = new Vector3(-xRange, transform.position.y, transform.position.z);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        // 오른쪽 경계를 넘어간 경우</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        else if (transform.position.x &gt; xRange)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            transform.position = new Vector3(xRange, transform.position.y, transform.position.z);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        // 경계 내부에 있는 경우</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        else</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            horizontalInput = Input.GetAxis("Horizontal");</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            transform.Translate(Vector3.right * Time.deltaTime * speed * horizontalInput);</t>
-  </si>
-  <si>
-    <t>Car Project PlayerController.cs *참고</t>
-  </si>
-  <si>
-    <t>1. 영역제한</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.local pc에 unity game 정보 저장하기. : PlayerPrefs 클래스 사용</t>
-  </si>
-  <si>
-    <t>local에 저장하면 좋은점</t>
-  </si>
-  <si>
-    <t>(1) 인터넷연결과 무관하다.</t>
-  </si>
-  <si>
-    <t>(2)프로그램 실행파일이 삭제되더라도 정보는 남아있다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3)변수와 다르게 게임실행이 종료되더라도 메모리에서 사라지지 않는다. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">로칼에 저장하기 </t>
-  </si>
-  <si>
-    <t>PlayerPrefs.SetFloat("PMJ", rr.time)</t>
-  </si>
-  <si>
-    <t>로칼에서 가져오기</t>
-  </si>
-  <si>
-    <t>best = PlayerPrefs.GetFloat("PMJ") + 0.2f;</t>
-  </si>
-  <si>
-    <t>2.분산버전관리 : Git(혼자할때) GitHub(팀으로 할때) 구글드라이브</t>
-  </si>
-  <si>
-    <t>버전간 다른부분만 히스토리로 저장한다. 그래서 저장용량을  아낄수 있고, 버전간 이동이 자유롭다.</t>
-  </si>
-  <si>
-    <t>2-1 구글드라이브 백업 tip</t>
-  </si>
-  <si>
-    <t>(1).unity project 백업시 불필요한 폴더들(library,logs,UserSettings,obj,Build(s),Temp)은 삭제</t>
-  </si>
-  <si>
-    <t>(2) 공유하는법 : 점 세개를 누른다음에 사람모양 클릭 -&gt; 공유받을 사람의 이메일 주소를 입력 -&gt; 권한을 설정한다 -&gt; 보낸다.</t>
-  </si>
-  <si>
-    <t>(3) 공유 받은것 사용법 : 내 드라이브로 간다음에 왼쪽에 공유 문서함 폴더 안에 있음.</t>
-  </si>
-  <si>
-    <t>Assets 메뉴 &gt; Import package &gt; Custom Package &gt; 파일선택</t>
-  </si>
-  <si>
-    <t>3. 로칼에 있는 유니티 패키지 파일(.unitypackage) 임포트 하는 방법</t>
-  </si>
-  <si>
-    <t>1.다이나믹(중력 O)에서 키네마틱(중력X, 외력X)으로 바꾸기.</t>
-  </si>
-  <si>
-    <t>private void OnCollisionEnter(Collision collision)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        print("hello");</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        GetComponent&lt;Rigidbody&gt;().isKinematic = true;</t>
-  </si>
-  <si>
-    <t>1-1 인스펙터창에서 바꾸는법(2차원) : rigidbody 2D 컴퍼넌트 -&gt; body type 클릭 -&gt; kinematic 선택</t>
-  </si>
-  <si>
-    <t>7.파티클 사용해서 이펙트 표시</t>
-  </si>
-  <si>
-    <t>(1)파티클 이펙트 = 작은 입자</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2) 파티클 이펙트 실행 ex) GetComponent&lt;ParticleSystem&gt;().Play(); </t>
-  </si>
-  <si>
-    <t>1. 제네릭, &lt;T&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1)제네릭이 필요한 이유 : 다양한 종류의 컴포넌트에 대응하는 범용 자료형이 필요하기 때문이다. </t>
-  </si>
-  <si>
-    <t>(2) 제네릭형식 ex) GetComponent&lt;T&gt;();</t>
-  </si>
-  <si>
-    <t>2.월드 좌표계와 스크린 좌표계</t>
-  </si>
-  <si>
-    <t>(1)월드 좌표계 : 오브젝트의 위치 좌표계값의 기준의 되는 좌표계. 즉 유니티 에디터에서 사용하는 좌표계(고정 좌표계)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1-1)하이러라키창에 루트오브젝트(최상위 위치)는 월드좌표계를 기준으로 하고 서브 오브젝트는 그 상위 오브젝트를 기준좌표계(상대 좌표계)로 한다. </t>
-  </si>
-  <si>
-    <t>(1-2)서브 오브젝트 주의사항 : 처음부터 서브를 구성하지 말것. 왜냐하면 상대좌표계로 위치값을 설정해야 하는데, 쉽지가 않기 때문이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1-3) center와 pivot 위치가 같은 오브젝트(유니티 기본 오브젝트)에서 pivot위치를 다른위치로 바꾸는 방법 </t>
-  </si>
-  <si>
-    <t>a : 빈오브젝트(empty)를 만든다 b : 원래오브젝트를 empty의 서브로 만든다 c : 서브가 된 원래오브젝트의 좌표값을 원하는 pivot위치가 되도록 변경한다</t>
-  </si>
-  <si>
-    <t>a -&gt; b -&gt; c의 순서로 진행</t>
-  </si>
-  <si>
-    <t>(2)스크린 좌표계 : 디바이스 화면상의 기준 좌표계. 유니티 에디터에서 사용하는 좌표계가 아니라 디바이스상의 좌표계</t>
-  </si>
-  <si>
-    <t>(3) ex) Ray ray= Camera.main.ScreenPointToRay(Input.mousePosition);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            Vector3 worldDir = ray.direction;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            Bam.GetComponent&lt;BamController&gt;().Shoot(worldDir.normalized * 2000);</t>
-  </si>
-  <si>
-    <t>(4)ScreenPointToRay 메소드는 카메라 위치를 원점기준으로 하는 메소드이다. 그러므로 카메라와 날라가려는 오브젝트의 원점이 다르면 조정을 해줘야한다.</t>
-  </si>
-  <si>
-    <t>2. out 한정자</t>
-  </si>
-  <si>
-    <t>(1). out 한정자는 매개변수중에 결과값을 전달받는 매개변수(return값과 유사함)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2) ex)  public static void Out(out int num,out string name) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">            num = 50;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            name = "hello";</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        static void Main(string[] args)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            int a;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            string name = "hi";</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            Out(out a, out name);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            Console.WriteLine("num :" + a + "name :" + name);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        }  // C#용 코드</t>
-  </si>
-  <si>
-    <t>1. Ray 형 오브젝트</t>
-  </si>
-  <si>
-    <t>(1) Ray형 오브젝트는 콜라이더와 리지드바디 모두 기본적으로 가지고 있다.</t>
-  </si>
-  <si>
-    <t>2.Raycast 메소드</t>
-  </si>
-  <si>
-    <t>(1) Raycast 메소드는 리턴값이 bool형이다.</t>
-  </si>
-  <si>
-    <t>(2)충돌이 일어나면 True를 반환하고 안일어나면 False를 반환한다.</t>
-  </si>
-  <si>
-    <t>(3)Raycast 메소드 두번째 매개변수는 RaycastHit형을 쓴다.</t>
-  </si>
-  <si>
-    <t>4. Unity API</t>
-  </si>
-  <si>
-    <t>링크 : https://docs.unity3d.com/ScriptReference/</t>
-  </si>
-  <si>
-    <t>3-1 에러가 발생한다면 Project창의 Assets &gt; Standard Asstes &gt; Utillity 에서 에러가 발생한 스크립트를 찾아서 지운다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3. RaycastHit</t>
-  </si>
-  <si>
-    <t>(1) RaycastHit은 Ray와 원점이 충돌한 지점의 정보를 가지고 있는 구조체 자료형</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2)세번째 매개변수 인자는 카메라와 닿는 물체사이의 거리를 구해서 설정해준다. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   하지만 Mathf.Infinity를 쓰면 거리가 무한대 이기에 편하다.</t>
-  </si>
-  <si>
-    <t>5. 코드 분석법</t>
-  </si>
-  <si>
-    <t>(1) 절차적으로 위에서 아래로 내려가면서 봐라.</t>
-  </si>
-  <si>
-    <t>(2) 의심스러운 부분(if문,메소드 등등) 은 갖다대서 메소드 원형을 찾아봐라</t>
-  </si>
-  <si>
-    <t>(3) 그 메소드가 뭐하는 애인지 알고싶으면 구글링(UnityAPI)을 해봐라. stackoverflow(코딩계의 네이버 지식인) 사이트 참고</t>
-  </si>
-  <si>
-    <t>(4)코드 중간중간에 이상이 있는 부분을 print로 값을 찍고, 확인과정을 거쳐라.</t>
-  </si>
-  <si>
-    <t>(5) 검증과정이 끝나면 print를 지우거나 주석처리를 해라.</t>
-  </si>
-  <si>
-    <t>(6)코드에다가 중요한부분이나 문제가 되는 부분에 매우 자세히 주석을 달아놔라.</t>
-  </si>
-  <si>
-    <t>(7)노트필기 말고도 코드자체에 주석(주석은 10년후의 내가 욕하지않게 자세히 쉽게 풀어서 쓸데없는 얘기까지)을 달아라.</t>
-  </si>
-  <si>
-    <t>(번외)스크립트의 성질과 안맞는 코딩을 하지말것(아무데서나 다 할수있지만 아무데나 하지말고 가장 어울리는 스크립트를 찾아라)</t>
-  </si>
-  <si>
-    <t>3.ScreenPointToRay</t>
-  </si>
-  <si>
-    <t>(1) MainCamera를 원점를 원점으로 하는 메소드 이다.</t>
-  </si>
-  <si>
-    <t>1.OnTriggerEnter 메소드</t>
-  </si>
-  <si>
-    <t>(1)매개변수 other의 의미 : 충돌한 상대 오브젝트.</t>
-  </si>
-  <si>
-    <t>(1) 의미 : 스크립트에서 오브젝트를 식별하기 위한 수단</t>
-  </si>
-  <si>
-    <t>1.Tags</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) 감각 저하</t>
-  </si>
-  <si>
-    <t>(2) 기억력 저하</t>
-  </si>
-  <si>
-    <t>(3) . ' . = 코딩 실력 저하</t>
-  </si>
-  <si>
-    <t>6.복붙을 하면 안돼는 이유</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)원인 : 포멧이 맞지 않는 오디오 파일</t>
-  </si>
-  <si>
-    <t>(2) 해결방법 : 유니티에서 사용가능한 포멧으로 변환해준다. 사이트 링크 : https://online-audio-converter.com 에서 에러가 발생하는 오디오 파일을 변환시켜 준다</t>
-  </si>
-  <si>
-    <t>1.리소스 오디오 클립 에러</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)public(프로퍼티의 set,get의 기본 접근 지정자)</t>
-  </si>
-  <si>
-    <t>(2)private(attr(필드,메소드,프로퍼티)의 기본 접근지정자)</t>
-  </si>
-  <si>
-    <t>(3)internal(클래스 기본 접근지정자)</t>
-  </si>
-  <si>
-    <t>3.접근지정자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)이 메소드를 호출하는 스크립트가 삭제되더라도 재생을 보장함</t>
-  </si>
-  <si>
-    <t>(2)해보니까 코루틴 안써도 딜레이 줄수있음</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ex ) </t>
-  </si>
-  <si>
-    <t>AudioSource.PlayClipAtPoint(clip, transform.position); //dodge 프로젝트 PlayerController.cs 55번 줄 참고</t>
-  </si>
-  <si>
-    <t>1.AudioSource.PlayClipAtPoint() 메소드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) 프레임 간격 사이에 경과 시간</t>
-  </si>
-  <si>
-    <t>(2)de += Time.deltaTime; //프레임간에 경과시간을 누적하여 더함.</t>
-  </si>
-  <si>
-    <t>1.time.deltaTime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.하이러라키 창에 존재하는 게임오브젝트와 프로젝트창에 리소스는 다르다.</t>
-  </si>
-  <si>
-    <t>=프로젝트창의 리소스는 게임오브젝트가 아니다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)보안무시하고 삭제하기 예시) DestroyImmediate(삭제 할 컴포넌트,true);</t>
-  </si>
-  <si>
-    <t>2.컴포넌트 삭제하는 방법</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)원인. 배열의 크기를 벗어나는 인덱스를 사용했다.</t>
-  </si>
-  <si>
-    <t>(2)해결법 : 25와 관련된 경우</t>
-  </si>
-  <si>
-    <t>if (AP.GetComponents&lt;Collider&gt;().Length != 0) //배열 사이즈를 체크해서 에러를 차단한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            DestroyImmediate(AP.GetComponents&lt;Collider&gt;()[0], true); //여기서 에러가 발생하는 경우</t>
-  </si>
-  <si>
-    <t>2.IndexOutOfRangeException: Index was outside the bounds of the array 에러 발생시 대처법</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) 기능 : 스크립트상에서 오브젝트의 컴포넌트를 추가해준다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2) 사용법 : gameObject.AddComponent(typeof(SphereCollider)); </t>
-  </si>
-  <si>
-    <t>(3) 잘못된 사용법 : gameObject.AddComponent( "SphereCollider" ) as SphereCollider; // 비추천 방식, 에러 가능성 있음(deprecated)</t>
-  </si>
-  <si>
-    <t>3.AddComponent 사용법</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) deprecated : 권장안함. 향후 버전에서 존재하지 않을수 있음.</t>
-  </si>
-  <si>
-    <t>(2) legacy :  이전버전과의 호환성이나 기타 이유로 유지됨(살아있음) 권장안함.</t>
-  </si>
-  <si>
-    <t>7. deprecated 와 legacy 의 차이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) 게임의 난이도를 조정하는 방법론 : 예시 오브젝트가 떨어지는 속도값, 어떤 오브젝트가 나올지 결정하는 확률값</t>
-  </si>
-  <si>
-    <t>(2) 레벨이란 : 게임의 스테이지 또는 난이도 등을 뜻함.</t>
-  </si>
-  <si>
-    <t>1.레벨 디자인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)Object 클래스의 메소드이다. 따라서 Object 클래스를 상속하고있기 때문에 어떤 자료형이든 쓸 수 있다.</t>
-  </si>
-  <si>
-    <t>(2)의미 : 참조변수를 문자열로 변환해준다.</t>
-  </si>
-  <si>
-    <t>(3)사용법 : float tume = 60.0f;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  tume.ToString("F1"); //Tume이 어떤자료형이든 Object 클래스의 메소드 이기 때문에 사용할 수 있다.  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">F1의 의미 : 소수점 한자리까지 표시 </t>
-  </si>
-  <si>
-    <t>F2라면 두자리 까지 표시</t>
-  </si>
-  <si>
-    <t>매개변수 인자를 안적으면 원래 자릿수로 변환한다.</t>
-  </si>
-  <si>
-    <t>31. 기본자료형</t>
-  </si>
-  <si>
-    <t>(1) 기본자료형은 이름이 바뀐 형태이고 실체는 구조체이다.</t>
-  </si>
-  <si>
-    <t>(2) 예시 : float형의 실체는 struct Single 이다. int형은 struct Int32이다.</t>
-  </si>
-  <si>
-    <t>(3) 왜 저렇게 이름을 했을까 : 개발자들이 저이름에 익숙해져있기 때문에.</t>
-  </si>
-  <si>
-    <t>4. ToString 메소드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) 의미 : 문자열끼리 더해서 새로운 문자열을 만들어 내는 방식 더하기 연산자 사용</t>
-  </si>
-  <si>
-    <t>(2) 예시 : PT.GetComponent&lt;Text&gt;().text = point.ToString()+ " point";</t>
-  </si>
-  <si>
-    <t>5. Concatenate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) 의미 : this가 쓰인 그 클래스의 인스턴스를 의미함(이 클래스의 부모 클래스의 인스턴스는 base로 표현함)</t>
-  </si>
-  <si>
-    <t>(2) 사용처 : 매개변수랑 필드의 이름이 같을땐 this를 사용하는걸 써야만 함</t>
-  </si>
-  <si>
-    <t>(2) 예시 :this.sp = sp;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">           this.speed = speed;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">           this.ratio = ratio; //좋은 사용 예</t>
-  </si>
-  <si>
-    <t>sp = sp</t>
-  </si>
-  <si>
-    <t>speed = speed;</t>
-  </si>
-  <si>
-    <t>ratio = ratio;  //나쁜 사용 예</t>
-  </si>
-  <si>
-    <t>6. this</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) 남아있는 컴퓨터 하드용량이 충분하지않으면 정상적인 빌드가 안될 수 있다.</t>
-  </si>
-  <si>
-    <t>3.안드로이드 빌드시 주의사항</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) 에러가 발생하면 콘솔창에 에러가 표시됨 단 에러가 해결이 되더라도 콘솔창에 남아있기 때문에 주의해야함.</t>
-  </si>
-  <si>
-    <t>4.unity 에러 표시 주의사항</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) 의미 : 텍스쳐(표면, 이미지) + 셰이더(색,질감,빛반사,굴절등)</t>
-  </si>
-  <si>
-    <t>(2) 만드는법 :프로젝트 창에서 우클릭을 한후 create -&gt; material 선택</t>
-  </si>
-  <si>
-    <t>3.머터리얼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>= 스케치 + 물감</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)center : 센터는 오브젝트의 중심점이 지형학적 중심</t>
-  </si>
-  <si>
-    <t>(2)pivot : 피봇은 발바닥이 기준점</t>
-  </si>
-  <si>
-    <t>4.center 와 pivot</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(1)project 창에서 해당스크립트파일을 선택 </t>
-  </si>
-  <si>
-    <t>(2)우클릭</t>
-  </si>
-  <si>
-    <t>(3)reimport 클릭</t>
-  </si>
-  <si>
-    <t>5. 유니티 스크립트 public field가 에디터에서 안보일때</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)리지드 바디 컴퍼넌트 드래그를 납득하지 못함. 따져보니까 그동안 스크립트는 아무 이질감없이 드래그 해왔음 스크립트도 컴퍼넌트임</t>
-  </si>
-  <si>
-    <t>따라서 컴퍼넌트도 오브젝트, 스크립트처럼 드래그 할 수 있다.</t>
-  </si>
-  <si>
-    <t>5.내가 햇갈렸던 것들</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) AddForce를 사용하게 되면 관성력이 작용되고 그상태에서 방향전환을 하려면 관성력을 이겨야 하기 때문에 조작감이 나쁘다. 하지만 실제물리현상을 구현한다.</t>
-  </si>
-  <si>
-    <t>(2) velocity를 사용하게 되면 물리현상의 결과값을 바꿀 수 있기 때문에 관성력이 작용하더라도 무시가 가능하다. 그러므로 조작감이 좋다. 하지만 비현실적이다.</t>
-  </si>
-  <si>
-    <t>2. Rigidbody 와 AddForce 메소드와 velocity의 차이점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) 의미 : GetAxis 의 매개변수값으로 문자열을 설정하게 되는데 그문자열은 edit -&gt; Project Settings -&gt; Input Manager -&gt; Axes 안에서 키별로 정의된 문자열들 중에서 선택해서 사용해야한다</t>
-  </si>
-  <si>
-    <t>즉 그 키를 조작했을때 GetAxis의 리턴값은 그 키가 Positve Button이면 0~1사이 값을 가지고 Negative Button 이면 0~(-1)사이 값을 가지고 그 키를 오래 누를수록 0에서 1또는 -1에 가까워 진다.</t>
-  </si>
-  <si>
-    <t>(1) edit -&gt; Project Settings -&gt; Input Manager -&gt; Axes 가서 size을 늘린다 맨마지막 스트링과 똑같은 복사본이 생긴다 그 복사본을 바꿔서 사용한다</t>
-  </si>
-  <si>
-    <t>(2-1) 주의점 : size 값이 axes 개수보다 작으면 axes가 삭제된다 따라서 함부로 size값을 줄이지 말자.</t>
-  </si>
-  <si>
-    <t>(2-2) 서로다른 Axes에 같은키를 배정하면 두Axes가 복수로 작동한다. 따라서 의도한게 아니라면 서로 다른 키값을 배정해 줘야 한다.</t>
-  </si>
-  <si>
-    <t>(2-3) 내가 만든 스크립트 말고 특정오브젝트는 오브젝트에서 자기 스스로 만들어 사용하는 스크립트가 존재한다. 그 스크립트 내부에서 Axes를 사용 할 수 있다. 예를 들면 UI를 사용하면 EventSystem 오브젝트</t>
-  </si>
-  <si>
-    <t>가 생기는데 얘가 StandaloneInputModule.cs가 생기고(내가 만든게 아님) 이안에서 Axes를 사용하고 있으므로 함부로 지우면 안된다. 만약에 지우면 ArgumentException: Input Button Submit is not setup~ 이런</t>
-  </si>
-  <si>
-    <t>에러가 발생한다(에러코드에서 나온 Submit Axes를 StandaloneInputModule.cs에서 사용하고 있기 때문에 함부로 지우면 안된다.)</t>
-  </si>
-  <si>
-    <t>4.Input.GetAxis 메소드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5. Axes 새로 만들기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) 의미 : 현실세계의 사물을 단순화 시킨모델 (메모리를 차지않음 실제로 존재X)</t>
-  </si>
-  <si>
-    <t>(2) 사용법 : 인스턴스(클래스를 복제해서 만든 것, 메모리에 존재함으로 클래스와 달리 실체가 있다)를 사용해서 구현</t>
-  </si>
-  <si>
-    <t>(3) 자료형 : 모든클래스는 자료형이 될 수 있다.</t>
-  </si>
-  <si>
-    <t>7.클래스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)의미 : 요소자료형이 다른 배열역할(메소드 포함)</t>
-  </si>
-  <si>
-    <t>7-1 구조체</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)클래스 : 인스턴스가 heap영역에 저장되고 구조체의 데이터는 변수공간에 직접 저장됨 구조체는 가비지 컬렉션이 필요없음(운영체제가 지움)</t>
-  </si>
-  <si>
-    <t>(1)동적인 특성(변수는 저장공간이 무조건 1개)이 없기 때문에 클래스로 만들 필요가 없고, 성능적으로 heap영역보다 stack영역에서 사용하는게 더 좋음 따라서 구조체로 만듦.</t>
-  </si>
-  <si>
-    <t>(1) 의미 : 인스펙터창의 오브젝트의 이름옆에 체크표시(활성화 여부, 활성화 : 화면상에서'만' 보이는지 안보이는지 여부, 하이러라키창에선 그대로 남아있음)를 스크립트에서 제어 하는 메소드</t>
-  </si>
-  <si>
-    <t>(2) ex : gameObject.SetActive(false);</t>
-  </si>
-  <si>
-    <t>7-2 클래스와 구조체의 차이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7-3 기본자료형을 구조체로 만든 이유</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.object.SetActive()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(1) 의미 : 첫번째 매개변수는 삭제 대상 오브젝트(하이러라키창에서도 삭제 즉 메모리에서 제거), 두번째 매개변수는 Destroy 메소드를 호출한시점에서 얼마뒤 삭제할건지 </t>
-  </si>
-  <si>
-    <t>(2) 사용예 : Destroy(gameObject, 3f); //이 스크립트를 가진 게임오브젝트를 삭제, 두번째 매개변수는 이 메소드가 호출되고 난뒤 3초뒤에 삭제</t>
-  </si>
-  <si>
-    <t>5.Destroy(Object x, float z);</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)의미 : 메소드의 이름은 같지만 매개변수의 자료형이 다르거나 개수가 다른 메소드</t>
-  </si>
-  <si>
-    <t>(2)오버로딩이 존재하는 이유 : 오버로딩이 없다면 바디의 작업처리과정은 유사하지만, 매개변수가 다르거나 자료형이 다른 메소드를 별개의 메소드로 구성해줘야 한다.(다형성)</t>
-  </si>
-  <si>
-    <t>(1)의미 : 부모의 메소드를 자식클래스에서 재정의 해서 사용하는것, 같은 이름의 메소드가 서로 다르게 작동하게 할 수 있음(다양함의 파생)</t>
-  </si>
-  <si>
-    <t>(2)주의점 : 자식클래스에서 오버라이딩된 부모 클래스의 메소드는 무력화 된다.</t>
-  </si>
-  <si>
-    <t>(3)base : 부모를 의미. super</t>
-  </si>
-  <si>
-    <t>(1) 의미 : 최소한의 코드를 가지고 다양한 기능을 구현한다.</t>
-  </si>
-  <si>
-    <t>(2) 다형성을 구현하는 방법 : 오버로딩, 오버라이딩 등등</t>
-  </si>
-  <si>
-    <t>8.오버로딩(overloading)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9. 오버라이딩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10. 다형성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) 의미 : 매개변수로 할당한 Transform 컴퍼넌트를 가지고 있는 오브젝트를 바라본다.</t>
-  </si>
-  <si>
-    <t>(2) 사용법 : bullet.transform.LookAt(target); //자세한 내용은 dodge 프로젝트에서 Spawner.cs 참고</t>
-  </si>
-  <si>
-    <t>(3) 대상오브젝트와 매개변수를 잇는 벡터가 대상오브젝트의 forward 프로퍼티가 된다.(dodge 프로젝트에서는 BulletController.cs의 forward값으로 사용된다.)</t>
-  </si>
-  <si>
-    <t>(1)의미 : T로(여기선 컴퍼넌트) 설정한 컴포넌트를 가진 오브젝트를 찾음 만약 컴포넌트를 가진 오브젝트가 존재 하지 않다면 예외(Exception)발생 예외는 런타임에러와 같다.</t>
-  </si>
-  <si>
-    <t>(1-2)스크립트내에서 다른오브젝트의 컴퍼넌트를 찾아야 할때 1.그 컴퍼넌트를 가진 오브젝트(GameObject.Find())를 써서 찾고, 2. 1번에서 찾은 object.GetComponuet() 써서 찾아야한다 그런데 이과정을 한번에 해주는 메소드다.</t>
-  </si>
-  <si>
-    <t>(2)사용예 :target = FindObjectOfType&lt;PlayerController&gt;().transform; //dodge프로젝트의 Spawner.cs 참고</t>
-  </si>
-  <si>
-    <t>6.대상오브젝트.transform.LookAt(Transform x, ); //오버로딩있음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7.FindObjectOfType&lt;T&gt;()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)의미 : 매개변수로 int 일때는 최대값 -1이고, float일때는 최대값도 포함해서 랜덤값을 리턴</t>
-  </si>
-  <si>
-    <t>11.Random.Range()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) 의미 : 이 스크립트를 가진 오브젝트가 Scene창에 나타날때 호출된다.(게임이 시작할때 무조건 실행X)</t>
-  </si>
-  <si>
-    <t>8.Start()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) 의미 : 프로그래밍에서 사용하는 Flag는 상태를 기록하고 제어하기 위한 boolean type(대체로 사용, 꼭 boolean을 사용할 필요 X)의 변수를 의미.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2) 예시 : </t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean flag = true; //초기값 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">while (flag) //초기에는 무한반복 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">      { </t>
-  </si>
-  <si>
-    <t xml:space="preserve">            input = scanner.nextInt();</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            if ((input % 2) == 0) {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                result += input;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">} </t>
-  </si>
-  <si>
-    <t>else { // else조건에 해당되는 순간 flag값이 바뀐다 따라서 무한반복이 종료되도록 처리함.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                System.out.println("======= " + input + " is Odd Number =======");</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                flag = false;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            }</t>
-  </si>
-  <si>
-    <t>12.flag 변수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)의미 : 유니티에서 제공해주는 데이터 배이스 '파일' 파일은 비휘발성인 HDD나 SSD에 저장된다(변수와 다르게 게임을 종료하거나 컴퓨터가 꺼져도 데이터 보존) 방대한 데이터는 저장용으로 적합하지않음</t>
-  </si>
-  <si>
-    <t>간단하고 개수가 적은 데이터들(예시 :게임정보, 상태정보) 저장하는데 사용 로컬에 저장되기 때문에 인터넷이 없더라도 사용가능</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2) 예시:   </t>
-  </si>
-  <si>
-    <t>if(surviveTime &gt; bestTime)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            bestTime = surviveTime;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            PlayerPrefs.SetFloat("BestTime", bestTime); //dodge프로젝트 gamedirector.cs 참고</t>
-  </si>
-  <si>
-    <t>(3)PlayerPrefs file 위치 : 윈도우 아이콘 우클릭 -&gt; 실행 -&gt; regedit 엔터 -&gt; HKEY_CURRENT_USER -&gt; Software -&gt; [company name] (만약 안적었다면 DefaultCompany) -&gt; [product name] (키값 이름 찾기)</t>
-  </si>
-  <si>
-    <t>텍스트로 저장이 아니라 바이너리(이진수)로 저장되어 있음.</t>
-  </si>
-  <si>
-    <t>9.PlayerPrefs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) 예시 : 서버에 정보저장할때 구글 파이어 베이스 등을 사용, 키 : 벨류 방식으로 저장하는 JSon</t>
-  </si>
-  <si>
-    <t>(1) 유니티 허브 실행 -&gt; Add 클릭 -&gt; 프로젝트 폴더 찾아서 오픈</t>
-  </si>
-  <si>
-    <t>8.서버</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9.유니티 허브에서 프로젝트 추가하는법</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)3차원에서 이미지파일 스프라이트 생성하는 방법 : 가져오려는 이미지를 assets창에 올린뒤 이미지 클릭 -&gt; 인스펙터 창에서 Texture type -&gt; Sprite(2D and UI) 선택 -&gt; save</t>
-  </si>
-  <si>
-    <t>(2)안되는 이유 : 2차원 파일에선 비트맵이 스프라이트인데 3차원프로젝트에서는 비트맵이 defalt 타입으로 설정되서 안된다. 왜 그렇게 설정이 되는 이유는 2차원에선 비트맵이 쓰이는 용도가</t>
-  </si>
-  <si>
-    <t>UI용 이미지로 사용되기 때문에 처음부터 UI용타입인 스프라이트로 만들어 주지만 3차원에선 비트맵의 용도가 UI용 이미지가 아니라 3차원 모델에 텍스쳐를 입히는 용도로 사용되기 때문에</t>
-  </si>
-  <si>
-    <t>defalt로 설정이 된다 따라서 UI용으로 사용하려면 수동으로 Spirte 타입으로 변경해야 한다.</t>
-  </si>
-  <si>
-    <t>6. 3차원 프로젝트에서 2d ui요소를 만들때 이미지 파일이 연결이 잘 안될때</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) dodge 프로젝트 PlayerCotroller.cs 참고</t>
-  </si>
-  <si>
-    <t>6.키보드 버튼대신 UI버튼으로 대체하는 방법</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)의미 : value : 제한하려는 값</t>
-  </si>
-  <si>
-    <t xml:space="preserve">           min :허용 가능한 최소값</t>
-  </si>
-  <si>
-    <t xml:space="preserve">           max :허용 가능한 최대값</t>
-  </si>
-  <si>
-    <t>만약 value가 min보다 작다면 min값으로 보정, max보다 크다면 max로 보정 min에서 max사이값이면 그대로</t>
-  </si>
-  <si>
-    <t>(2)주의사항 : value값이 최소한 min과 max범위 중심으로 움직이는값을 해야한다 범위가 완전 다른값한테 쓰면 엉뚱한 값이 나올 수 있다. 따라서 어느정도 범위에 맞게 적용해놔야한다. dodge button UI 조정성</t>
-  </si>
-  <si>
-    <t>문제 발생(speed 값이 8로 했더니 이상했고 50정도로 했더니 해결됨)</t>
-  </si>
-  <si>
-    <t>10.mathf.clamp(float value,float min,float max)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)의미 : 크기 + 방향을 두가지 물리량을 가지고 있음 (예: 속도,가속도,무게,힘...)</t>
-  </si>
-  <si>
-    <t>(2)정규화된 벡터(normalized vector) : 크기가 1인 단위벡터,방향벡터라고도 부른다.</t>
-  </si>
-  <si>
-    <t>(3)단위벡터 만드는법 : 단위벡터 = 벡터/벡터 크기(벡터크기 구하는법 : sqrt(벡터의 x성분^2 + 벡터의 y성분^2))</t>
-  </si>
-  <si>
-    <t>(3-1) 유니티 단위벡터 구하는법 : vector? 형 참조변수.normalized //?에는 Vector2,Vector3 등이 들어감 , Vector?형 참조변수.magnitude //벡터의 크기</t>
-  </si>
-  <si>
-    <t>(4)벡터의 합과 차를 구하는법 : 성분(x좌표끼리, y좌표끼리)끼리 더하거나 뺀다</t>
-  </si>
-  <si>
-    <t>(4-1) 유니티 합과 차 구하는 법 : Vector?형 참조변수 = Vector?형 참조변수 + Vector?형 참조변수</t>
-  </si>
-  <si>
-    <t>(5)벡터의 내적 : 내적값에 의해서 두벡터가 이루는 사잇각상태(몇도의 각을 갖고있는지)를 알아낼 수 있다.</t>
-  </si>
-  <si>
-    <t>(5-1) 유니티 벡터 내적 구하는법 : float c = Vector3.Dot(a,b); // Vector3.Dot() 는 두벡터(a,b)의 내적 구하는 메소드 구글드라이브의 벡터 표 참고</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6)벡터의 외적 : 두벡터가 이루는 평면이 수직의 벡터, 법선벡터(normal vector) </t>
-  </si>
-  <si>
-    <t>(6-1) 유니티 벡터 외적 구하는법 : Vector3 c = Vector3.Cross(a,b)</t>
-  </si>
-  <si>
-    <t>(6-2) 외적을 이용한 지면 식별 알고리즘</t>
-  </si>
-  <si>
-    <t>private void OnCollisionEnter2D(Collision2D collision) {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        // 바닥에 닿았음을 감지하는 처리</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        if (collision.contacts[0].normal.y &gt; 0.7f) //지면감지 알고리즘 : 지면의 이루는 각도가 45도 이하인 완만한 지면만 취급하는경우(벽,천장을 걸러낼 수 있다.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            isGrounded = true;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            jumpCount = 0;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   }</t>
-  </si>
-  <si>
-    <t>(7)모든벡터는 방향벡터 * 스칼라곱(배율)로 표현할 수 있다.</t>
-  </si>
-  <si>
-    <t>(7-1)유니티 스칼라곱 하는법 : Vector?형 참조변수 = Vector?형 * 스칼라값</t>
-  </si>
-  <si>
-    <t>(8) 유니티에서 벡터의 크기 구하는법 : float c = Mathf.Sqrt(0.27f * 0.27f + 0.53f * 0.53f + 0.8f * 0.8f); //Math.Sqrt 는 root</t>
-  </si>
-  <si>
-    <t>(9) 두벡터의 거리구하는 방법 : float d = Vector3.Distance(a, b); //거리만 관심있을때</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(10)회전량을 나타내는 자료형 : Quaternion(쿼터니언 으로 발음) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(10-1) 회전에서 벡터를 쓸 수 없는 이유 : 두축이상의 동시 회전 계산 시 짐벌락 현상 오류 발생 두축이상 동시 회전 계산이 가능하도록 만들어 진게 쿼터니언이다. </t>
-  </si>
-  <si>
-    <t>(10-2) 벡터 to 쿼터니언 사용법 : Quaternion rotaion = Quaternion.Euler(new Vector3(0,60,0)); // rotaion은 참조변수, 스크립트창에서 로테이션값을 변경해야할때 사용</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(10-3) 쿼터니언 to 벡터 사용법: Vector3 eulorRotation = rotaion.eulerAngles; // eulorRotation는 참조변수 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(10-4) 쿼터니언을 알아야 하는 이유 : 유니티 에디터에서 벡터3로 입출력을 처리해주지만 예를 들어서 trasform.rotation 같은 프로퍼티는 자료형이 Vector3가 아니라 Quaternion이기 때문에 쿼터니언에 대해서 </t>
-  </si>
-  <si>
-    <t>알고있어야 한다.</t>
-  </si>
-  <si>
-    <t>1.vector</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)의미 : 크기 한가지 물리량만 가지고 있음(방향없음) (예: 질량,거리...)</t>
-  </si>
-  <si>
-    <t>2.scalar</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)DEG(도) : degree (각도단위)</t>
-  </si>
-  <si>
-    <t>(2)RAD : radian (각도단위) 180도 = 파이rad</t>
-  </si>
-  <si>
-    <t>10. 계산기 약자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(1)전역변수(월드좌표계) 기준으로 동작하게 하는법 : 4번째 매개변수 인자로 Space.World를 넣어주면 됨 </t>
-  </si>
-  <si>
-    <t>11. 유니티 Transform 클래스 메소드(예 : Translate,Rotate...) defalt값(4번째 매개변수인자가 Space.Self로 설정)이 지역변수(지역좌표계 기준)으로 동작함</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)C#같은 언어는 코드가 클래스 내부에서만 존재할 수 있다. 하지만 어떤 클래스에도 소속되지않는 attribute(필드,메소드 등)들은 원래는 클래스없이 만들어져야하는데 하지만 C#의 특성으로 인해</t>
-  </si>
-  <si>
-    <t>반드시 어떤 클래스 내부에서 만들어져야 하므로 아무 상관도없는 어떤 클래스 내부에 구성될 수 밖에 없다. 그런 attribute들은 소속클래스와 연관이 없음을 명시적으로 표시하기 위해서 static선언을 한다</t>
-  </si>
-  <si>
-    <t>(2) 따라서 static attribute들은 클래스의 인스턴스를 통해서 사용되는건 모순이다 C#에서는 static attribute들은 소속클래스 이름.static attribute 형식을 통해서 사용되어야 함</t>
-  </si>
-  <si>
-    <t>다른방식(인스턴스를 통한)을 사용하면 에러가 남(Java같은 언어에서는 허용함)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3)static으로 선언된 attribute들은 RAM안에서 인스턴스내부가 아니라 DATA영역에 저장됨. 한번생기면 다신 안생김 </t>
-  </si>
-  <si>
-    <t>(4) Main에 선언된 static의 의미 : 만약 Main에 static이 안붙어있다면 Main메소드가 메모리에 올라가기 위해서 가장먼저 Main메소드를 포함하고 있는 클래스 인스턴스가 만들어져야 한다(New 연산자 사용)</t>
-  </si>
-  <si>
-    <t>인스턴스를 만들 주체가 없기 때문에 호출을 못하기 때문에 불가능하다 따라서 Main이 메모리에 못올라간다 이 프로그램을 실행했을때 O/S가 메인을 찾아야 하는데 Main이 없기 때문에 프로그램 실행이 안됨</t>
-  </si>
-  <si>
-    <t>따라서 Main에 static선언을 해줌으로써 프로그램 실행시 자동으로 가장먼저 메모리영역에 저장되도록 해주는 것이다. 두번째의미는 Main 메소드 특성상 프로그램의 시작과 끝을 지정해주는 메소드기 때문에</t>
-  </si>
-  <si>
-    <t>어느 클래스소속이라는게 어울리지 않는다 따라서 static선언을 해줌으로써 어떤 클래스와의 소속감을 분리시켜 준다. 그래서 static선언을 해주는게 어울린다.</t>
-  </si>
-  <si>
-    <t>13. static 선언</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.transform.position으로 값을 설정받을때 우항의 값은 전역공간 기준의 값으로 처리된다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.transform.localPosition으로 값을 설정받을때 우항의 값은 현재 좌표계를 기준으로 처리된다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) 프로퍼티 : 로컬좌표계용 프로퍼티가 따로존재함(ex : local~~~)</t>
-  </si>
-  <si>
-    <t>(2)메소드 : 메소드의 매개변수는 무조건 로컬좌표계로 처리한다</t>
-  </si>
-  <si>
-    <t>5.transform.rotation으로 값을 설정받을때 우항의 값은 전역공간 기준의 값으로 처리된다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6.transform.localRotation으로 값을 설정받을때 우항의 값은 현재 좌표계를 기준으로 처리된다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7.transform.Translate()메소드로 값을 설정받을때 매개변수 값은 현재 좌표계를 기준으로 처리된다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8.transform.Rotate()메소드로 값을 설정받을때 매개변수의 값은 현재 좌표계를 기준으로 처리된다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9.transform의 메소드와 프로퍼티 좌표계 기준</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7.씬창에서 오브젝트 배치할때 무조건 루트위치에서 위치를 결정한후에 그다음에 서브로 옮기는짓을 맨마지막으로 한다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)asset의 속성정보(인스펙터창의 속성항목 값들)을 저장하는 파일이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2)유니티 에디터에선 보이지 않는다 </t>
-  </si>
-  <si>
-    <t>(3)meta파일을 지워버리면 그 에셋은 default값을 가진다.</t>
-  </si>
-  <si>
-    <t>8.meta파일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">        Vector3.forward : new Vector3(0,0,1) :고정좌표계를 기준으로 한다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Vector3.back</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Vector3.up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Vector3.down</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Vector3.left</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Vector3.right</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transform.forward : </t>
-  </si>
-  <si>
-    <t>transform.back :</t>
-  </si>
-  <si>
-    <t>transform.up</t>
-  </si>
-  <si>
-    <t>transform.down</t>
-  </si>
-  <si>
-    <t>transform.left</t>
-  </si>
-  <si>
-    <t>transform.right</t>
-  </si>
-  <si>
-    <t>10.Vector3 구조체의 속기(shorthand)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11.transform 프로퍼티의 속기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)에셋폴더에서 스프라이트 선택</t>
-  </si>
-  <si>
-    <t>(2)인스펙터창에서 스프라이트 모드를 Multiple 선택후 apply버튼 클릭</t>
-  </si>
-  <si>
-    <t>(3)sprite editer 버튼을 눌러서 에디터창 띄우기</t>
-  </si>
-  <si>
-    <t>(4)slice 메뉴 선택 가로,세로 크기가 결정되있는 이미지들은 grid by cell size 선택후 낱개 이미지들의 가로,세로 픽셀값을 입력한후 slice버튼을 눌러 쪼갠다.</t>
-  </si>
-  <si>
-    <t>(4-2)(원본이미지 파일 우클릭 -&gt; 속성에서 픽셀사이즈를 체크한후 정확히 얼마로 쪼개야할지 체크해본다)</t>
-  </si>
-  <si>
-    <t>(5)스프라이트 가져와서 사용할때, 메타파일이 있다면 같이가져와야 자르는 작업을 편하게 할 수 있다(메타파일안에 자르기정보도 같이 포함되있기 때문이다)</t>
-  </si>
-  <si>
-    <t>1.spirt sheet 쪼개기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)유니티에서 Scene에 마이크 역할을 한다.</t>
-  </si>
-  <si>
-    <t>(2)Scene내에서 발생하는 모든 소리를 녹음한다. 즉 Audio Listener컴퍼넌트가 비활성화 되면 Scene내에서 발생하는 소리를 녹음할 수 없기 때문에 게임시작시 아무소리도 안들리게 된다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3)유니티에서는 Scene하나에 Audio Listener가 한개만 작동함 </t>
-  </si>
-  <si>
-    <t>2.Audio Listener 컴퍼넌트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)75번과정을 통해서 스프라이트 쉬트(sheet)를 쪼갠다.</t>
-  </si>
-  <si>
-    <t>(2)Window -&gt; Animation -&gt; Animation -&gt;하이러라키창에서 에니메이션을 적용할 오브젝트 선택 -&gt; Create -&gt;에니메이션 클립이름 정해서 저장</t>
-  </si>
-  <si>
-    <t>(3)스프라이트 쉬트를 끌어서 타임라인에 배치 -&gt; 타임라인 오른쪽상단 점세개를 클릭 -&gt; Show sample rate 선택 -&gt; 재생하고 samples값을 조정하여 적당한값을 결정</t>
-  </si>
-  <si>
-    <t>(1)에니메이터 창에서 드래그 하는방법 : 가운데 휠버튼 누른상태로 이동</t>
-  </si>
-  <si>
-    <t>(2)유니티에서의 유한상태머신의 상태의 의미 = 애니메이션클립</t>
-  </si>
-  <si>
-    <t>(3)Entry : 게임이 시작되면 엔트리에서 나가는쪽의 연결된 상태(애니메이션)가 실행된다(기본상태) (연결하고싶은 상태를 우클릭후 -&gt; Set as Layer Default State)</t>
-  </si>
-  <si>
-    <t>(4)any state : 화살표조건(현재상태는 상관X)만 만족하면 연결된 상태로 바로 바뀜</t>
-  </si>
-  <si>
-    <t>(5)Exit : exit는 exit에서 나가는화살표(Make Transition존재안함)를 못만들고 들어가는 화살표만 만들수 있다.(exit는 마지막으로 실행되는 상태이므로 exit에서 다른상태로 전이가 안된다) 잘사용X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6)화살표 지우는법 : 지우고자하는 화살표 클릭 -&gt; 키보드 "Delete"키 </t>
-  </si>
-  <si>
-    <t>(7)파라미터(애니메이터창에서 조건만들때 쓰이는변수) 만드는법 : 애니메이터창 왼쪽상단 Parameters 탭 클릭 -&gt; +버튼클릭 -&gt; 파라미터 자료형선택후 생성(이름은 임의로)</t>
-  </si>
-  <si>
-    <t>(7-1)파라미터의 오른쪽 체크표시는 게임이 실행되고 나서 유니티가 관리한다.</t>
-  </si>
-  <si>
-    <t>(8)화살표 조건 만드는법 :(8(</t>
-  </si>
-  <si>
-    <t>(9)has exit time 의미 : 체크를하면 settings에 exit time을 설정할수있는데, 조건을 만족해도 exit time을 채운뒤에 전이된다.(딜레이시간동안 이전의 애니메이션이 계속 실행)</t>
-  </si>
-  <si>
-    <t>(10)Transition Duration 의미 : 블렌딩시간(두 애니메이션의 중간 과정)을 설정, 2차원에선 지원안됨</t>
-  </si>
-  <si>
-    <t>(11)Conditions :  +버튼을 누르면 (7)에서 만들어뒀던 파라미터들을 이용해서 조건을 구성하면 된다. 그리고 파라미터의 값들은 스크립트코드에서도 사용가능</t>
-  </si>
-  <si>
-    <t>(12)Animator 클래스형 참조변수.SetBool() 메소드 : 첫번째 매개변수는 애니메이터창에있는 파라미터를 뜻함 두번째 매개변수로 첫번째 매개변수값에 대입 ex) animator.SetBool("Grounded", isGrounded);</t>
-  </si>
-  <si>
-    <t>(13)Animator 클래스형 참조변수.SetTrigger() 메소드 : 매개변수로 들어간 트리거형 파라미터를 활성화시킴</t>
-  </si>
-  <si>
-    <t>(14)Text애니메이션 만드는 예 : Window -&gt; Animation -&gt; Animation -&gt; 하이러라키창에서 에니메이션을 적용할 오브젝트 선택 -&gt; Create -&gt; add property -&gt; 오브젝트 별로 제공되는 프로퍼티중에 내가 활용할 프로퍼티를 선택한다(예 : gameobject형의 position)</t>
-  </si>
-  <si>
-    <t>2.에니메이션 스프라이트 쉬트로 에니메이션 클립 만들기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.유한상태머신(finite state machine)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) 생성자를 호출해서 인스터스를 만드는 시점 : 리소스를 씬으로 드래그하는순간. 그결과물로 만들어진 인스턴스들의 목록을 보여주는게 하이러라키창이다</t>
-  </si>
-  <si>
-    <t>(2)awake 콜백시점 : 씬창에 있는 오브젝트들이 전부 로딩된후. start()보다 빠른호출을 보장함. 그러므로 필드 초기화할때 유용함.</t>
-  </si>
-  <si>
-    <t>12. Awake()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)리턴값없이 함수를 종료하는역할 : if문의 바디안에서 함수를 종료해야할 필요가 있을때 리턴을 써야 함수가 끝남.</t>
-  </si>
-  <si>
-    <t>14.return()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)마우스버튼을 누르다가 땐순간 1번만 호출</t>
-  </si>
-  <si>
-    <t>13.Input.GetMouseButtonUp()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)2 by 3 의미 : 화면을 씬창,게임창,하이러라키창으로 나눔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.코류틴이 아닌 방법으로 딜레이 주기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)Invoke() 메소드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2)예시 : Invoke("lobby1", 3.0f); // 3초후에 lobby1 이라는 메소드를 호출한다. 주의사항 첫번째 매개변수 자료형은 문자열(메소드 이름)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3)주의사항 : 한프로젝트안에 같은 컴퍼넌트 이름이 2개 이상 존재할때 사용하면 안됨(왜냐하면 같은것을 참조하기때문), 고유한 이름의 컴퍼넌트를 찾을때만 사용할것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>(2)default 의미 : 기본창</t>
-  </si>
-  <si>
-    <t>9.Layer 오른쪽끝에있는 버튼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.창 추가하는법 : 씬창 우클릭 -&gt; add tap -&gt; 추가하고싶은 창 선택</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) == 연산자 : 기본자료형일땐 값을 비교 레퍼런스(클래스)형일땐 주소값비교(C언어는 클래스자료형이 없기 때문에 데이터비교할때도 쓰고 포인터 변수의 주소값 비교할때도 쓴다.)</t>
-  </si>
-  <si>
-    <t>(2) equals메소드 : 레퍼런스형 변수의 데이터 비교할때(C언어는 클래스를 사용하지 않으므로 해당안됨)</t>
-  </si>
-  <si>
-    <t>15. ==연산자와 equals메소드 차이점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)의미 : 충돌할때 생기는 배열</t>
-  </si>
-  <si>
-    <t>(2)배열의 인덱스로 0번을 주로 쓴다 왜냐하면 현실적으로 동시에 두개이상의 충돌포인트를 갖는게 힘들기 때문이다.</t>
-  </si>
-  <si>
-    <t>(3)ex ) private void OnCollisionEnter2D(Collision2D collision) {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1)의미 : 어떤 동일한 오브젝트가 대량으로 사용될때 사용한다. 또는 비슷한애지만 조금의 변형이 있는 오브젝트 씬에 존재하지않는 프리팹은 인스턴스가 아니다. </t>
-  </si>
-  <si>
-    <t>얘를 사용해서 작업처리를 하고싶으면 먼저 인스턴스화 시킨다음에 사용해야 한다. 예를 들면 Instanitiate()를 사용하여 구현</t>
-  </si>
-  <si>
-    <t>(2)만드는법 : 하이러라키창에 있는 오브젝트를 프로젝트창에 옮긴후 -&gt; 코드에서 작성 -&gt; 퍼블릭 필드에 프로젝트로 옮긴 오브젝트를 연결해준다.</t>
-  </si>
-  <si>
-    <t>(3)코드 : PublicAPIAttribute GameObject Spike;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        float span = 1.0f;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        float delta = 0;</t>
-  </si>
-  <si>
-    <t>private void Update() {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        delta += Time.deltaTime;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        if(DeltaSpeed &gt; span)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            DeltaSpeed = 0;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            GameObject go = Instantiate(spike);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            int px = Random.Range(-6, 7);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            go.transform.position = new Vector3(px,7,0);</t>
-  </si>
-  <si>
-    <t>}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.collision.contact[] </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15. Prefabs(프리팹 복제)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)주의사항 : 2D프로젝트에서는 콜백안됨.</t>
-  </si>
-  <si>
-    <t>(2)2D프로젝트에선 2D형 컴퍼넌트,메소드를 사용할것 예외는 vector3</t>
-  </si>
-  <si>
-    <t>2.OnCollisionEnter()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)SortingLayer로 정렬하기 : Sprite Renderer 컴퍼넌트 -&gt; Sorting Layer -&gt; Add Sorting Layer -&gt; +버튼클릭 -&gt; Layer추가(숫자가 높을수록 앞에 있고 낮을수록 가려진다) -&gt;각 오브젝트 선택후Sorting Layer값선택</t>
-  </si>
-  <si>
-    <t>11.레이어로 정렬하기(오브젝트들이 화면에 겹쳐지는 순서)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)오브젝트 크기구하는 방법 : 콜라이더를 씌워본다. -&gt; 콜라이더의 사이즈값을 체크한다 ex) 사각형오브젝트에 박스콜라이더를 씌워서 사이즈 체크</t>
-  </si>
-  <si>
-    <t>2.배경이어붙이기(Crankie Box)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)메인 카메라 -&gt; background -&gt; 스포이드 눌러서 배경색 찍기</t>
-  </si>
-  <si>
-    <t>12.메인카메라 배경</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)stackoverflow</t>
-  </si>
-  <si>
-    <t>(2)github</t>
-  </si>
-  <si>
-    <t>11.개발자가 알아야하는 사이트 목록</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(1)Canvas 오브젝트 선택 -&gt; 인스펙터창에서 Canvas Scaler 컴퍼넌트의 UI Scale Mode를 scale with screen size 선택 -&gt; 내가 설치하려는 디바이스 해상도를 입력(비율로 적어도 OK) </t>
-  </si>
-  <si>
-    <t>(2)UI Scale Mode를 Constant Pixel Size로 선택하면 유니티에디터에서 보이는대로 안보일 확률이 크다 따라서 scale with sreen size를 선택해야 한다.(가장 선호도높은 디바이스를 찾은뒤 걔를 기준으로 UI를 구성한다)</t>
-  </si>
-  <si>
-    <t>1. 유니티 에디터에서 보이는대로 실제 디바이스에서 UI가 보이게 하는 방법(유니티에디터에서는 실제디바이스에서 보이는거랑 다를 수 있다.)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(1)모니터 픽셀 하나하나에 컬러값(RGBA A는 투명도)을 구하는 연산순서를 정의한것 따라서 이순서에 맞춰 연산을 해야된다. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">예 )60Hz짜리 해상도 1920X1080 모니터의 경우 픽셀이 약 207만개, 60분의 1초마다 207만개의 픽셀의 컬러값을 계산해야 한다. 이계산과정은 GPU에서 수행한다. </t>
-  </si>
-  <si>
-    <t>예) 고성능 게임의 경우(조명환경이 복잡하거나 시시각각으로 환경이 변하는 경우) 각픽셀에 컬러값을 계산하는데 굉장히 많은 연산작업이 필요하게 된다. 따라서 모니터 주파수 60분의 1초마다 출력해야하는데</t>
-  </si>
-  <si>
-    <t>그걸 처리못해 버벅거리는 현상이 버퍼링 현상이다.</t>
-  </si>
-  <si>
-    <t>1. 렌더링 파이프라인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)기본적으로 scale with size모드를 사용해야 하며, 해상도 비율이 다른 디바이스에 대응하기 위해 UI 요소들으 배치가 가로방향 위주이면 Match값을 width &gt; height로 구성해주고, 세로방향 위주이면</t>
-  </si>
-  <si>
-    <t>Match값을 width &lt; height로 구성해준ㄴ다. 동일한 해상도 비율의 디바이스 간에는 Match값이 의미가 없음 Match값은 유니티 에디터에서 기준으로 삼은 해상도 비율과 다른 디바이스에 해당 앱이</t>
-  </si>
-  <si>
-    <t>설치되었을때 UI의 배치가 어떤식으로 조정할것인지에 대한 factor(어떤요인이 되는 변수)값임 따라서, 유니티 에디터에서 기준으로 삼은 해상도 비율과 일치하는 디바이스에서는 Match값은 의미가 없다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.Canvas 옵션설정 방법 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)메모리상에 오직 인스턴스가 하나만 존재해야 하는 클래스 (예를들면 장치의 부품들처럼 하나만 존재하는 부품을 소스코드에서 가져다 사용해야 될 경우 그부품 클래스의 인스턴스가 여러개 존재하는것은 모순이다.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2)만드는 방법 : 생성자를 private으로 만든다( private Store() { } ) -&gt; static 필드로 객체 생성(  private static   Store instance = new Store(); ) </t>
-  </si>
-  <si>
-    <t>-&gt; 객체의 getter 구현( public static Store getInstance() {return instance}</t>
-  </si>
-  <si>
-    <t>(3)유니티에서 싱글톤 만드는법 :</t>
-  </si>
-  <si>
-    <t>16.싱글톤(single tone)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)추상클래스는 추상메소드(추상메소드는 바디가없고 선언부만 있는 메소드)를 가지고있는 클래스</t>
-  </si>
-  <si>
-    <t>(2)추상클래스를 상속한 자식클래스에서 그 추상메소드를 오버라이딩해서 추상메소드를 사용할 수 있는 메소드로 만든다.(구현) extends사용</t>
-  </si>
-  <si>
-    <t>(3)단,  자식클래스에서 추상클래스의 추상메소드를 오버라이딩 할 의무는 없다(선택이다  extends 사용)</t>
-  </si>
-  <si>
-    <t>(1)상수,추상메소드(추상메소드는 바디가없고 선언부만 있는 메소드)만 가지고있는 클래스 필드,일반메소드는 존재할 수 없음.</t>
-  </si>
-  <si>
-    <t>(2)자식인터페이스에서 상속 가능(extends) 자식인터페이스끼리 상속</t>
-  </si>
-  <si>
-    <t>(3)자식클래스에서 상속하는경우 반드시 추상클래스의 추상메소드를 의무적으로 구현해줘야함(implements 사용)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4)추상클래스와의 차이점 : 추상메소드의 구현을 자식클래스에서 강제적으로 하면 인터페이스, 선택이면 추상클래스 이다. 그리고 추상클래스와 인터페이스는 공통적으로 다형성(오버라이딩,오버로딩) 구현의 수단이다. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">다만 인터페이스가 추상클래스보다 더 강제성을 띈다. </t>
-  </si>
-  <si>
-    <t>(1)사용법 : 참조변수.GetHashCode()</t>
-  </si>
-  <si>
-    <t>17.추상 클래스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>18.인터페이스(interface)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>19.인스턴트의 주소값을 알려주는 메소드(GetHashCode())</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)의미 : 게임시작시 필요한 오브젝트를 미리 만들어서 특정영역(게임화면 밖)에 배치해두고 필요할때마다 갖다쓰고 다쓰면 원래위치로 반환 게임실행중에 해당오브젝트가 새로 생성되거나 삭제되지 않는다.</t>
-  </si>
-  <si>
-    <t>(2)프리팹공장 방식과의 차이점 : 오브젝트를 미리만들지않고 게임실행중에 필요할때마다 Instantiate()를 사용해서 복제하고 필요없으면 Destroy()메소드로 삭제한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3)장단점 : 장점은 게임실행중에 삭제(가비지 컬렉션)작업이 없기 때문에 쾌적하다. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">단점 : 게임시작시에 오브젝트를 만드는데 로딩시간이 필요하다.(프리팹공장방식에선 Destroy()메소드를 호출하여 삭제하는것이 실질적으로는 가비지컬렉션 작업이 발생하는것 이며 가비지컬렉션은 </t>
-  </si>
-  <si>
-    <t>메인쓰레드(어떤 주작업영역(UI나 핵심적인 작업등)상에서 작업처리가 되기 때문에 게임이 중지된다. 사용자가 느끼기에 버퍼링이 생기는것 처럼 느끼게 된다.)</t>
-  </si>
-  <si>
-    <t>3.오브젝트 풀링(object pooling)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)특징 : 배열인데도 배열명이 상수가 아니라 참조변수이다.</t>
-  </si>
-  <si>
-    <t>(2)만드는법 : GameObject[] platforms = new GameObject[count]; // new연산자를 사용한다. 즉 우항의 배열공간이 heap영역에 생긴다. 그리고 그것뿐만이 아니라 결론적으로 클래스 인스턴스 처럼 생긴다. 그안에 배열데이터가 들어간다</t>
-  </si>
-  <si>
-    <t>20. c#에서의 배열</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LLVM ERROR: IO failure on output stream: No space left on device</t>
-  </si>
-  <si>
-    <t>PLEASE submit a bug report to https://github.com/android-ndk/ndk/issues and include the crash backtrace.</t>
-  </si>
-  <si>
-    <t>Stack dump:</t>
-  </si>
-  <si>
-    <t>Program arguments: "C:/Program Files/Unity/Hub/Editor/2022.3.17f1/Editor/Data/PlaybackEngines/AndroidPlayer/NDK/toolchains/llvm/prebuilt/windows-x86_64/bin/llvm-objcopy.exe" --only-keep-debug Library/Bee/artifacts/Android/libunity/armeabi-v7a/unstripped/libunity.so Library/Bee/artifacts/Android/libunity/armeabi-v7a/libunity.dbg.so</t>
-  </si>
-  <si>
-    <t>UnityEngine.GUIUtility:ProcessEvent (int,intptr,bool&amp;)</t>
-  </si>
-  <si>
-    <t>(1)원인 : 하드용량 부족</t>
-  </si>
-  <si>
-    <t>(2)대처법 : 이런 에러싸인이 나오면 pc의 하드용량이 모자란지 확인해본다. 하드용량을 충분히 잡아준뒤 다시 빌드한다.</t>
-  </si>
-  <si>
-    <t>(1)원인 : 같은 프로젝트안에 동명의 Camera 스크립트가 존재 하기때문(Camera.mainScreenToWorldPoint(Input.mousePosition); 이 메소드를 호출할때 유니티에서 제공하는 Camera클래스와 이름이 같기때문에 에러가 발생)</t>
-  </si>
-  <si>
-    <t>(2)대처법 : 유니티 라이브러리에서 제공하는 클래스이름과 같은 이름으로 스크립트를 만들지 않는다.(좋은이름 짓는 방법 : 지으려는 이름에 _자기이름을 같이 사용한다거나 해서 겹치지않게 한다.)</t>
-  </si>
-  <si>
-    <t>6.Building Library\Bee\artifacts\Android\libunity\armeabi-v7a\libunity.dbg.so failed with output:</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6-1 Assets\Script\slingShotScript.cs(32,50): error CS0117: 'Camera' does not contain a definition for 'main'</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)의미 : 매개변수로 설정한 디바이스상(스크린좌표계,픽셀단위를 사용)의 좌표를 유니티의 월드좌표계(유니티 자체 단위계(눈금))로 변환해준다 단, Z값은 카메라의 Z값으로 반환 즉 카메라랑 선상에 있어서 안보인다</t>
-  </si>
-  <si>
-    <t>(2)대처법 : 2D일때는 vector2로 명시적형변환을 해준다.</t>
-  </si>
-  <si>
-    <t>(2-1) 예시 스크립트 : transform.position = (Vector2)Camera.main.ScreenToWorldPoint(Input.mousePosition);</t>
-  </si>
-  <si>
-    <t>7. Camera.main.ScreenToWorldPoint();</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)의미 :  오브젝트의 궤적(발자취)을 그려주는 컴퍼넌트</t>
-  </si>
-  <si>
-    <t>(2)사용법</t>
-  </si>
-  <si>
-    <t>(2-1) Materials : 설정안하면 기본값으로 보라색 색종이(사각형)으로 나옴 머터리얼을 다른값으로 설정하면 머터리얼대로 나옴 단, 레이어 정렬이 적용되는것과 안되는것이 있음 적용되는것은 파티클만 가능</t>
-  </si>
-  <si>
-    <t>1.Trail Renderer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)setActive는 GameObject클래스 소속의 메소드고 GameObject클래스 + 상속한 자식클래스의 참조변수에서만 사용할 수 있다. 따라서 GameObject와 상속관계가 없는 Component형 참조변수(예 : TraillRenderer)를 통해서는 호출 할 수 없다</t>
-  </si>
-  <si>
-    <t>(2)따라서 Component형 참조변수를 활성화시키거나 비활성화 시킬때는 SetActive를 사용할 수 없고, Component클래스에서 제공하는 enabled 프로퍼티를 사용해서 활성화,비활성화 처리를 할 수있다.</t>
-  </si>
-  <si>
-    <t>16. setActive와 Enabled의 차이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)동기식(sync) : 동기식은 메소드가 호출되면 메소드가 실행종료될때까지 다음라인으로 안넘어가고 대기상태</t>
-  </si>
-  <si>
-    <t>(2)비동기식(async) : 비동기식은 메소드호출되고 메소드의 종료 여분상관없이 다음라인으로 넘어감 (예시: StartCoroutine)</t>
-  </si>
-  <si>
-    <t>21.메소드의 동작방식(동기식,비동기식)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(1)GameObject클래스와 아무런 상속관계가 없다. 따라서 서로간에 형변환이 불가능하다. </t>
-  </si>
-  <si>
-    <t>(2)하지만 Unity에서는 Scene에 추가된 모든자로형은 GameObject형으로도 취급되므로 형변환이 가능하다. UNITY에서만 해당</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.UI 자료형(예 : Slider) </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(1)힘의 공식 : F = ma // f는 힘,m은 질량, a는 가속도 </t>
-  </si>
-  <si>
-    <t>(1)E = mc^2 // E는 에너지,m는 질량,c는 광속도</t>
-  </si>
-  <si>
-    <t>(1) 하는법 :</t>
-  </si>
-  <si>
-    <t>3.뉴턴의 운동방정식</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 5.Rigidbody 컴퍼넌트 질량값 조절</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.아인슈타인의 에너지 공식</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1) if(!(collision.gameObject.tag.Equals("Ground"))) //코드의 맨앞부분에 적는다 햇갈린다면 ()를 사용해서 명시적으로 구분을 해줄것</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            x.SetTrigger("New Trigger");</t>
-  </si>
-  <si>
-    <t>22. !(not) 붙이는위치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)일단 필요한 자료형 이름을 소스코드에 적는다(using이 안되있다면 빨간줄이 그어진다)</t>
-  </si>
-  <si>
-    <t>(2)빨간줄 그어지고 빨간색 X아이콘이 나타나고 그걸 클릭한다</t>
-  </si>
-  <si>
-    <t>(3)목록으로 오류사항을 해결할수 있는 해결책을 제시해준다 그중에서 선택한다.</t>
-  </si>
-  <si>
-    <t>1.자료형의 namespace가 기억안날때</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)https://jinhyo98.tistory.com/436 참고</t>
-  </si>
-  <si>
-    <t>12.폴더내 특정 키워드를 가진 파일찾기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)게임오브젝트 : 유니티 내에서 사용하는 고유 좌표계</t>
-  </si>
-  <si>
-    <t>(2) UI : 스크린좌표계(픽셀)</t>
-  </si>
-  <si>
-    <t>4. 게임오브젝트와 UI단위계(좌표계) 차이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>public class Score : MonoBehaviour</t>
-  </si>
-  <si>
-    <t>{</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    GameObject G;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Text T;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    // Start is called before the first frame update</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    void Start()</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        G = GameObject.Find("small_helmet_pig_sprites_by_chinzapep-d57z4bs_0");</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        print(gameObject);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        T = GetComponent&lt;Text&gt;(); //26번 라인의 RectTransform형 position 프로퍼티를 사용하기 위해서 찾는다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                  //왜냐하면 gameobject형에서는 RectTransform을 쓸수 없기 때문이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        print(T);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        T.rectTransform.position = Camera.main.WorldToScreenPoint(G.transform.position);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    } /* scene좌표계의 돼지좌표값을 UI좌표계로 변환한 우항의 값을 Text UI좌표값으로 대입을 시키려면 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">       * 좌항의 UI의 좌표값(position)으로 UI의 좌표계 자료형인 RectTransform형 position 프로퍼티를 사용해야 한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       * 만약 Transform형 position 프로퍼티를 좌항에서 사용하면 Text UI좌표값이 정상적으로 설정되지 못한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       * 왜냐하면 Transform형 position 프로퍼티는 게임오브젝트의 위치값을 설정할때 사용하는 프로퍼티이고 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">       * UI의 위치값을 설정할때는 사용할 수 없기 때문이다 UI의 위치값을 설정할때는 반드시 RectTransform형</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       * position 프로퍼티를 사용해야 한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       */</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. Scene좌표계와 월드좌표계 변환방법 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(4)gameObject.Find() : 게임오브젝트만 찾아준다. 그리고 비활성 상태의 오브젝트는 못찾는다. 비활성화된 오브젝트를 찾는방법은 여러가지가 있지만 가장 간단한건 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스크립트코드에서 public GameObject 형 필드를 만들고 에디터에서 해당 비활성 오브젝트를 드래그해서 연결해준다.(유니런에서 사용한 방법)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2119,107 +2146,107 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
@@ -2227,42 +2254,42 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -2278,27 +2305,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -2314,382 +2341,382 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B29" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B49" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B50" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B51" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.4">
@@ -2697,247 +2724,247 @@
         <v>5</v>
       </c>
       <c r="B93" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B94" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -2953,22 +2980,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>
@@ -2979,412 +3006,427 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{194DBF29-D361-403B-8094-6B4DBAD9B202}">
-  <dimension ref="A1:A98"/>
+  <dimension ref="A1:A103"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>230</v>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>236</v>
+        <v>535</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A34" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A35" t="s">
-        <v>251</v>
+        <v>536</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A38" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>258</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>255</v>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>14</v>
+        <v>253</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>257</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>277</v>
+        <v>255</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>271</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A51" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>276</v>
+        <v>270</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>312</v>
+        <v>272</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>311</v>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A59" t="s">
-        <v>382</v>
+        <v>275</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A62" t="s">
-        <v>388</v>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>387</v>
+        <v>383</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A64" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A66" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A69" t="s">
-        <v>290</v>
+        <v>386</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>291</v>
+        <v>411</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>11</v>
+        <v>394</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>292</v>
+        <v>395</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>293</v>
+        <v>396</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>14</v>
+        <v>289</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>294</v>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A76" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>414</v>
+        <v>291</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>399</v>
+        <v>292</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>400</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A81" t="s">
-        <v>402</v>
+        <v>293</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>404</v>
+        <v>397</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A84" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A89" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>412</v>
+        <v>406</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A95" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>486</v>
+        <v>408</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>484</v>
+        <v>409</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>485</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A99" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A101" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A102" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A103" t="s">
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -3400,52 +3442,52 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -3461,167 +3503,167 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>390</v>
+        <v>534</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -3637,242 +3679,242 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -3888,67 +3930,67 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
   </sheetData>
@@ -3964,57 +4006,57 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -4030,47 +4072,47 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -4086,277 +4128,277 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -4372,137 +4414,137 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -4513,7 +4555,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9A39CD-5B16-41A0-8B36-B999957D39DD}">
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -4548,7 +4590,7 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>529</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
@@ -4558,17 +4600,17 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
@@ -4578,37 +4620,52 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>532</v>
       </c>
     </row>
   </sheetData>
@@ -4624,272 +4681,272 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
@@ -4899,42 +4956,42 @@
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.4">
@@ -4944,47 +5001,47 @@
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -5000,22 +5057,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -5031,27 +5088,27 @@
   <sheetData>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -5067,12 +5124,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
@@ -5082,82 +5139,82 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>

--- a/유니티_노트.xlsx
+++ b/유니티_노트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1F75D5-C249-4DA9-BF57-A5FA8603B8FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40ACB955-5E5D-4C2F-91F0-77E115B01078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" activeTab="12" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" firstSheet="2" activeTab="5" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
   </bookViews>
   <sheets>
     <sheet name="디버깅" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="531">
   <si>
     <t>1.딜레이 주는 방식</t>
   </si>
@@ -71,6 +71,9 @@
     <t xml:space="preserve">        </t>
   </si>
   <si>
+    <t xml:space="preserve">        SceneManager.LoadScene("GameScene");</t>
+  </si>
+  <si>
     <t xml:space="preserve">    }</t>
   </si>
   <si>
@@ -1290,6 +1293,9 @@
     <t>(1)2 by 3 의미 : 화면을 씬창,게임창,하이러라키창으로 나눔</t>
   </si>
   <si>
+    <t>(2)default 의미 : 기본창</t>
+  </si>
+  <si>
     <t>9.Layer 오른쪽끝에있는 버튼</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1701,6 +1707,9 @@
     <t xml:space="preserve">    void Start()</t>
   </si>
   <si>
+    <t xml:space="preserve">        G = GameObject.Find("small_helmet_pig_sprites_by_chinzapep-d57z4bs_0");</t>
+  </si>
+  <si>
     <t xml:space="preserve">        print(gameObject);</t>
   </si>
   <si>
@@ -1738,42 +1747,6 @@
   </si>
   <si>
     <t xml:space="preserve">8. Scene좌표계와 월드좌표계 변환방법 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">        G = GameObject.Find("small_helmet_pig_sprites_by_chinzapep-d57z4bs_0");</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">        SceneManager.LoadScene("GameScene");</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.코류틴이 아닌 방법으로 딜레이 주기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1)Invoke() 메소드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(2)예시 : Invoke("lobby1", 3.0f); // 3초후에 lobby1 이라는 메소드를 호출한다. 주의사항 첫번째 매개변수 자료형은 문자열(메소드 이름)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(3)주의사항 : 한프로젝트안에 같은 컴퍼넌트 이름이 2개 이상 존재할때 사용하면 안됨(왜냐하면 같은것을 참조하기때문), 고유한 이름의 컴퍼넌트를 찾을때만 사용할것</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(2)default 의미 : 기본창</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(4)gameObject.Find() : 게임오브젝트만 찾아준다. 그리고 비활성 상태의 오브젝트는 못찾는다. 비활성화된 오브젝트를 찾는방법은 여러가지가 있지만 가장 간단한건 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스크립트코드에서 public GameObject 형 필드를 만들고 에디터에서 해당 비활성 오브젝트를 드래그해서 연결해준다.(유니런에서 사용한 방법)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2146,107 +2119,107 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
@@ -2254,42 +2227,42 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
@@ -2305,27 +2278,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -2341,382 +2314,382 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B29" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B49" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B50" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B51" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.4">
@@ -2724,247 +2697,247 @@
         <v>5</v>
       </c>
       <c r="B93" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B94" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -2980,22 +2953,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -3006,427 +2979,412 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{194DBF29-D361-403B-8094-6B4DBAD9B202}">
-  <dimension ref="A1:A103"/>
+  <dimension ref="A1:A98"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
-        <v>533</v>
+        <v>230</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>535</v>
+        <v>236</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>536</v>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>234</v>
+        <v>253</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>258</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A41" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>253</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>10</v>
+        <v>257</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>271</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>257</v>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A54" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>272</v>
+        <v>312</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A57" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>275</v>
+        <v>384</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A61" t="s">
-        <v>310</v>
+        <v>383</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A64" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>382</v>
+        <v>413</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A66" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>386</v>
+        <v>398</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A69" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>411</v>
+        <v>291</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>394</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>395</v>
+        <v>292</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>396</v>
+        <v>293</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>289</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A76" t="s">
-        <v>10</v>
+        <v>294</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>291</v>
+        <v>414</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>292</v>
+        <v>399</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>13</v>
+        <v>400</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>293</v>
+        <v>401</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A81" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A84" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>402</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A89" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A95" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>408</v>
+        <v>486</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>409</v>
+        <v>484</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A99" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A101" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A102" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A103" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -3442,52 +3400,52 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -3503,167 +3461,167 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>534</v>
+        <v>390</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -3679,242 +3637,242 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>
@@ -3930,67 +3888,67 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
   </sheetData>
@@ -4006,57 +3964,57 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -4072,47 +4030,47 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -4128,277 +4086,277 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -4414,137 +4372,137 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -4555,7 +4513,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9A39CD-5B16-41A0-8B36-B999957D39DD}">
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -4590,7 +4548,7 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>529</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
@@ -4600,17 +4558,17 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
@@ -4620,52 +4578,37 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
-        <v>532</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -4681,272 +4624,272 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
@@ -4956,42 +4899,42 @@
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.4">
@@ -5001,47 +4944,47 @@
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -5057,22 +5000,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -5088,27 +5031,27 @@
   <sheetData>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -5124,12 +5067,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
@@ -5139,82 +5082,82 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>

--- a/유니티_노트.xlsx
+++ b/유니티_노트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CodingScience\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0840C41-6523-457D-9CE7-7C857227A956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93C2BD4-3EBC-4DC3-9766-A8133C9C7CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" activeTab="3" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="788">
   <si>
     <t>1.딜레이 주는 방식</t>
   </si>
@@ -2693,6 +2693,46 @@
   </si>
   <si>
     <t>smooth, auto는 자동조정할때 쓰인다)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(5-7)node(절점)옮기는법 : node를 수정하려면 slice tool을 해제한상태에서 해야한다(slice tool이 켜져있으면 파란색 테투리때문에 못옮긴다),움직일 노드를 선택후 드래그</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(5-9)노드와 노드사이에 선을 만들고 싶을떄 : 두개의 노드중에서 하나는 클릭, 하나는 shift + 클릭을 하면 두개의 노드가 서로 연결된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(5-10)노드 weight tool쓸때 주의사항 : 노드를 두개이상잡고 가중치를 설정하면 전체 가중치에 영향이 가므로 주의</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(5-8)노드 추가,삭제하는 방법 : 노드와 노드사이의 선중간에 추가할떄는 shift + 클릭, 내부에서 추가할땐 더블클릭, 노드를 지울떈 지울 노드를 선택후 delete키, 노드 두개를 선택하면 전체선택을 의미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(4-2)애니메이션을 설정할떄 애니메이션을 에니메이션창에서 바로 설정 하지말고, 씬창에서 transform값을 변경하면서 결과값을 본뒤에 적용하면 편하다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(4-3)애니메이션 값 설정할때 주의사항 :  애니메이션 설정할때 버그나서 값이 설정되지 않을땐 애니메이션창을 끄고 다시 키면 된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(6-1)리깅(rigging) : 애니메이션을 위한 뼈대구성법, 리깅의 종류에는 FK(Forward Kinematics), IK(inverse Kinimatics)이 있다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(6-2)FK(Forward kinematics) : 아무 설정도 안하면 나오는 기본값이다. 부모뼈의 종속관계에 의해서 자식뼈의 위치가 자동으로 정해지는 방식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(6-3)IK(Inverse Kinematics) : 특정 조인트(관절)의 포지션을 내가 설정하고싶을때(position만값만 설정가능,rotation와 scale은 설정만되고 적용이 안됨) 사용하는 방식(주로 팔,다리같은 부위에 사용한다),이외에 나머지 특징은 FK와 같다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(6-4)리깅의 우선순위 : 어떤 스프라이트메시의  FK와 IK가 동시에 설정됬을때 IK먼저 적용되고 FK는 적용되지 않는다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2807,6 +2847,50 @@
         <a:xfrm>
           <a:off x="7620" y="11049000"/>
           <a:ext cx="1809524" cy="504762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>8561</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>214045</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>548574</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>131706</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74CF5A24-698E-65B7-7D8D-01F40B5C92A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8561" y="15351303"/>
+          <a:ext cx="5214755" cy="3256762"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7857,7 +7941,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{077E7B44-DC3A-4864-9EC7-4ADF55F1E293}">
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B110"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -8100,114 +8184,200 @@
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>765</v>
+        <v>782</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A58" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A59" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A60" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A61" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A64" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A65" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A66" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A67" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A68" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A69" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A64" s="1" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A70" s="1" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A65" s="1" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A71" s="1" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A66" s="1" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A72" s="1" t="s">
         <v>775</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A67" s="1" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A73" s="1" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A68" s="1" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A74" s="1" t="s">
         <v>777</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A69" s="1"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A70" s="1"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A71" s="1"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A72" s="1"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A73" s="1"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A74" s="1"/>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A75" s="1" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A76" s="1"/>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A77" s="1"/>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A78" t="s">
+      <c r="A78" s="1"/>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A79" s="1"/>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A80" s="1"/>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A81" s="1"/>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A82" s="1"/>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A83" s="1"/>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A84" s="1"/>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A85" s="1"/>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A86" s="1"/>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A87" s="1"/>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A88" s="1"/>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A89" s="1"/>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A90" s="1"/>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A91" s="1" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A92" s="1" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A93" s="1" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A94" s="1"/>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A95" s="1" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A96" s="1" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A97" s="1" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A98" s="1" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A99" s="1"/>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A100" s="1"/>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A104" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A79" t="s">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A105" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A80" t="s">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A82" t="s">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A108" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A83" t="s">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A84" t="s">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A110" t="s">
         <v>753</v>
       </c>
     </row>

--- a/유니티_노트.xlsx
+++ b/유니티_노트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CodingScience\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93C2BD4-3EBC-4DC3-9766-A8133C9C7CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF11D67-B5BA-4846-8D3E-32DE5D21CACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="970" activeTab="3" xr2:uid="{B02B6B7F-B5FB-499D-9AFB-39DA46038C86}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="794">
   <si>
     <t>1.딜레이 주는 방식</t>
   </si>
@@ -2733,6 +2733,30 @@
   </si>
   <si>
     <t>(6-4)리깅의 우선순위 : 어떤 스프라이트메시의  FK와 IK가 동시에 설정됬을때 IK먼저 적용되고 FK는 적용되지 않는다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(6-5) IK 설정법 : </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spritemesh에 적용하는게 아니라 뼈에 적용하는것이다. IK가 적용되야할 뼈가 아니라 그위의 부모뼈를 선택한후 -&gt; 우클릭 -&gt; IK limb 클릭(동그라미의 원점위치가 조인트에 오는지 확인)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(6-6) : Ik Limb 2D 컴퍼넌트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>//orient Child : 체크하면 마지막뼈의 rotation값이 변하지않는다(회전을 막는다)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>//record : 체크하면 매번 애니메이션을 실행할때 연산을 하지않고 미리 계산된 값을 쓴다(게임성능이 좋아진다)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>//flip : 현재 회전값의 반대의 값을 적용한다</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2891,6 +2915,94 @@
         <a:xfrm>
           <a:off x="8561" y="15351303"/>
           <a:ext cx="5214755" cy="3256762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>17125</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>17124</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>417685</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>205483</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7AED40E-33A5-B126-1059-EA0907BAA214}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17125" y="22055191"/>
+          <a:ext cx="2404021" cy="1969213"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>17124</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>335936</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>150556</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="그림 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33C57319-F484-97B3-01E5-84CE362EDE39}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="24281259"/>
+          <a:ext cx="4342857" cy="1914286"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7941,7 +8053,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{077E7B44-DC3A-4864-9EC7-4ADF55F1E293}">
-  <dimension ref="A1:B110"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -8335,49 +8447,119 @@
         <v>785</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A97" s="1" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A98" s="1" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A99" s="1"/>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A99" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="C99" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A100" s="1"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A104" t="s">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A101" s="1"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A102" s="1"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A103" s="1"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A104" s="1"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A105" s="1"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A106" s="1"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A107" s="1"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A108" s="1"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A109" s="1" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A110" s="1"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A111" s="1"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A112" s="1"/>
+      <c r="H112" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A113" s="1"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A114" s="1"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A115" s="1"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A116" s="1"/>
+      <c r="H116" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A117" s="1"/>
+      <c r="H117" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A118" s="1"/>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A122" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A105" t="s">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A123" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A106" t="s">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A124" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A108" t="s">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A126" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A109" t="s">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A127" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A110" t="s">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A128" t="s">
         <v>753</v>
       </c>
     </row>
